--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2661,6 +2661,1248 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ML_064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Message List with Composer</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify sent message from composer appears in message list</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a message in composer.
+2. Send.
+3. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Sent message should immediately appear in message list at the bottom with correct content and timestamp.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ML_065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Message List with Conversation List</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list updates reflect in conversation list preview</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Go back to conversation list.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Conversation preview should show the latest sent message text and updated timestamp.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ML_066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Message List with User Profile</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify tapping user avatar opens user profile</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Tap on a user's avatar in message list.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>User profile/info panel should open with user details.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ML_067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Message List with Real-time Events</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Verify real-time message delivery from another user</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. User B sends a message to User A.
+2. Observe User A's message list.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Message should appear in real-time without manual refresh.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ML_068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Verify typing indicator in message list</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. User B starts typing.
+2. Observe User A's chat.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Typing indicator (e.g., 'User B is typing...') should appear and disappear when typing stops.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ML_069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Message List with Read Receipts</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Verify read receipts (double tick/blue tick)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Receiver reads it.
+3. Observe sender's message.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Message should show read receipt indicator (blue double tick or similar).</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ML_070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Verify delivered receipt (single/double tick)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Message gets delivered but not read.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Message should show delivered indicator (double grey tick or similar).</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ML_071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Regression: Message List after actions</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list intact after editing a message</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit a message.
+2. Observe entire message list.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Only edited message should change. All other messages should remain intact with correct order.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ML_072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list intact after deleting a message</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete a message.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Deleted message should be removed/replaced. All other messages unaffected.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ML_073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list after switching between conversations</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation A.
+2. Switch to conversation B.
+3. Switch back to A.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Conversation A should reload with correct messages. No message mixing between conversations.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ML_074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list after app backgrounding and resuming</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a chat.
+2. Background the app for 5 minutes.
+3. Resume.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Message list should refresh with any new messages received while backgrounded.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ML_075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Security: Message List</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Verify messages only visible to conversation participants</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as User A.
+2. Open a conversation with User B.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ML_076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Verify message content not exposed in URL or logs</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Send messages.
+2. Check browser URL bar and console logs.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ML_077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Security: Message List</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in message display</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
+2. Observe in receiver's message list.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ML_078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Verify SQL injection prevention in messages</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Message should display as plain text. No database errors or data loss.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ML_079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with malicious URL</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with a phishing/malicious URL.
+2. Observe link preview.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ML_080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list with 10000+ messages in conversation</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a conversation with 10000+ messages.
+2. Scroll through.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ML_081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with only whitespace/spaces</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with only spaces.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Message should either be blocked from sending or display as empty bubble.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ML_082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with mixed RTL and LTR text</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Text should render correctly with proper bidirectional formatting.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ML_083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with 50+ emojis</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with 50+ emojis.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>All emojis should render correctly. No performance issues or layout breaking.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ML_084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Verify simultaneous messages from multiple users in group</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1. Have 10 users send messages simultaneously in a group.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ML_085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with extremely long single word (no spaces)</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with a 1000-character word with no spaces.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ML_086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list when WebSocket disconnects</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate WebSocket disconnection during active chat.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ML_087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list with corrupted/invalid message data</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate receiving a message with missing or malformed fields.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ML_088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Boundary: Message List</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a single character 'a'.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Message should display correctly in a properly sized bubble.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ML_089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with maximum allowed characters</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Message should send and display correctly. May need 'Read more' expansion.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ML_090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Verify message at character limit + 1</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ML_091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Verify reaction with maximum number of unique reactions</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Add the maximum number of different reaction emojis to a single message.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ML_092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list with exactly 0 messages (new conversation)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a brand new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display. Composer should be ready for first message.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ML_093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Message Types</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Verify short text message (1-50 chars)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with 25 characters.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Message should display in a compact bubble.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ML_094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Verify medium text message (51-500 chars)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with 250 characters.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Message should display in a medium-sized bubble with proper wrapping.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ML_095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Verify long text message (501-5000 chars)</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with 2500 characters.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Message should display with 'Read more' or expandable view.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ML_096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Verify very long text message (5000+ chars)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message with 10000 characters.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Message should handle gracefully with expansion option. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ML_097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Media Sizes</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Verify small image (&lt;100KB)</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Send an image under 100KB.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Image should upload quickly and display as thumbnail.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ML_098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Verify medium image (100KB-5MB)</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Send an image of 2MB.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Image should upload with progress indicator and display correctly.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ML_099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Verify large image (5MB-25MB)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Send an image of 15MB.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Image should upload with progress bar. May take longer. Should complete successfully.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ML_100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Verify oversized image (&gt;25MB or above limit)</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to send an image exceeding the file size limit.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display. File should not upload.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Message List Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,10 +439,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,9 +547,9 @@
           <t>ML_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify sender message alignment (right side)</t>
@@ -571,9 +578,9 @@
           <t>ML_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify receiver message alignment (left side)</t>
@@ -602,9 +609,9 @@
           <t>ML_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify user name displayed above messages</t>
@@ -633,9 +640,9 @@
           <t>ML_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify user avatar displayed next to messages</t>
@@ -664,9 +671,9 @@
           <t>ML_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify message timestamp display</t>
@@ -695,9 +702,9 @@
           <t>ML_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify date separator between different days</t>
@@ -726,9 +733,9 @@
           <t>ML_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify scroll to load older messages</t>
@@ -757,9 +764,9 @@
           <t>ML_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify auto-scroll to latest message on open</t>
@@ -787,9 +794,9 @@
           <t>ML_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify new incoming message auto-scrolls</t>
@@ -860,8 +867,8 @@
           <t>ML_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
@@ -938,9 +945,9 @@
           <t>ML_014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify multiple reactions on a message</t>
@@ -968,9 +975,9 @@
           <t>ML_015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify reaction count increments</t>
@@ -998,9 +1005,9 @@
           <t>ML_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify removing own reaction</t>
@@ -1028,9 +1035,9 @@
           <t>ML_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify reaction details/list</t>
@@ -1144,9 +1151,9 @@
           <t>ML_020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify reply shows original message preview</t>
@@ -1175,9 +1182,9 @@
           <t>ML_021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify sending a reply message</t>
@@ -1207,9 +1214,9 @@
           <t>ML_022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify tapping on replied message scrolls to original</t>
@@ -1237,9 +1244,9 @@
           <t>ML_023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verify cancel reply</t>
@@ -1311,9 +1318,9 @@
           <t>ML_025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify thread panel opens on 'Reply In Thread'</t>
@@ -1341,9 +1348,9 @@
           <t>ML_026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply count on parent message</t>
@@ -1372,9 +1379,9 @@
           <t>ML_027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Verify clicking thread count opens thread</t>
@@ -1445,9 +1452,9 @@
           <t>ML_029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Verify copying text message</t>
@@ -1561,9 +1568,9 @@
           <t>ML_032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Verify editing a message</t>
@@ -1593,9 +1600,9 @@
           <t>ML_033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Verify cancel edit</t>
@@ -1710,9 +1717,9 @@
           <t>ML_036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Verify message info shows delivery details</t>
@@ -1740,9 +1747,9 @@
           <t>ML_037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Verify message info in group shows read/delivered by</t>
@@ -1813,9 +1820,9 @@
           <t>ML_039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Verify delete confirmation dialog</t>
@@ -1843,9 +1850,9 @@
           <t>ML_040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Verify message deleted on confirm</t>
@@ -1873,9 +1880,9 @@
           <t>ML_041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Verify cancel delete keeps message</t>
@@ -1946,8 +1953,8 @@
           <t>ML_043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
@@ -2024,9 +2031,9 @@
           <t>ML_045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Verify notification tap opens correct conversation</t>
@@ -2055,8 +2062,8 @@
           <t>ML_046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open in foreground</t>
@@ -2176,9 +2183,9 @@
           <t>ML_049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Verify video call button in chat header</t>
@@ -2207,9 +2214,9 @@
           <t>ML_050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Verify initiating audio call from chat</t>
@@ -2237,9 +2244,9 @@
           <t>ML_051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr"/>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Verify initiating video call from chat</t>
@@ -2267,8 +2274,8 @@
           <t>ML_052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
@@ -2345,9 +2352,9 @@
           <t>ML_054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Verify member join/leave messages in chat</t>
@@ -2376,9 +2383,9 @@
           <t>ML_055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Verify admin action messages in chat</t>
@@ -2450,9 +2457,9 @@
           <t>ML_057</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Verify image message display</t>
@@ -2481,9 +2488,9 @@
           <t>ML_058</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Verify video message display</t>
@@ -2512,9 +2519,9 @@
           <t>ML_059</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Verify audio message display</t>
@@ -2543,9 +2550,9 @@
           <t>ML_060</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Verify document/file message display</t>
@@ -2574,9 +2581,9 @@
           <t>ML_061</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Verify link preview in message</t>
@@ -2605,9 +2612,9 @@
           <t>ML_062</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Verify sticker message display</t>
@@ -2636,9 +2643,9 @@
           <t>ML_063</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Verify emoji-only message display</t>
@@ -2661,1243 +2668,1645 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ML_064</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Message List with Composer</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify sent message from composer appears in message list</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Type a message in composer.
 2. Send.
 3. Observe message list.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sent message should immediately appear in message list at the bottom with correct content and timestamp.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ML_065</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Integration: Message List with Conversation List</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message list updates reflect in conversation list preview</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Go back to conversation list.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Conversation preview should show the latest sent message text and updated timestamp.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ML_066</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Integration: Message List with User Profile</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify tapping user avatar opens user profile</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Tap on a user's avatar in message list.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>User profile/info panel should open with user details.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_067</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Integration: Message List with Real-time Events</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify real-time message delivery from another user</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. User B sends a message to User A.
 2. Observe User A's message list.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Message should appear in real-time without manual refresh.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ML_068</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr"/>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify typing indicator in message list</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. User B starts typing.
 2. Observe User A's chat.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Typing indicator (e.g., 'User B is typing...') should appear and disappear when typing stops.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ML_069</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr"/>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Integration: Message List with Read Receipts</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify read receipts (double tick/blue tick)</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Receiver reads it.
 3. Observe sender's message.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Message should show read receipt indicator (blue double tick or similar).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ML_070</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify delivered receipt (single/double tick)</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Message gets delivered but not read.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Message should show delivered indicator (double grey tick or similar).</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ML_071</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Message List after actions</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify message list intact after editing a message</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Edit a message.
 2. Observe entire message list.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Only edited message should change. All other messages should remain intact with correct order.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ML_072</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message list intact after deleting a message</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Delete a message.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Deleted message should be removed/replaced. All other messages unaffected.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ML_073</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify message list after switching between conversations</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Open conversation A.
 2. Switch to conversation B.
 3. Switch back to A.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Conversation A should reload with correct messages. No message mixing between conversations.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_074</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify message list after app backgrounding and resuming</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Open a chat.
 2. Background the app for 5 minutes.
 3. Resume.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Message list should refresh with any new messages received while backgrounded.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ML_075</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Message List</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify messages only visible to conversation participants</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login as User A.
 2. Open a conversation with User B.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ML_076</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message content not exposed in URL or logs</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send messages.
 2. Check browser URL bar and console logs.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ML_077</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Security: Message List</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify XSS prevention in message display</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
 2. Observe in receiver's message list.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_078</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify SQL injection prevention in messages</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Message should display as plain text. No database errors or data loss.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ML_079</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify message with malicious URL</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with a phishing/malicious URL.
 2. Observe link preview.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Link should be clickable but app should warn about external links or have URL validation.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ML_080</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Message List</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify message list with 10000+ messages in conversation</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation with 10000+ messages.
 2. Scroll through.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ML_081</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message with only whitespace/spaces</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with only spaces.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message should either be blocked from sending or display as empty bubble.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ML_082</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr"/>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify message with mixed RTL and LTR text</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Text should render correctly with proper bidirectional formatting.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_083</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify message with 50+ emojis</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with 50+ emojis.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All emojis should render correctly. No performance issues or layout breaking.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ML_084</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify simultaneous messages from multiple users in group</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Have 10 users send messages simultaneously in a group.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ML_085</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify message with extremely long single word (no spaces)</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with a 1000-character word with no spaces.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ML_086</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Message List</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify message list when WebSocket disconnects</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Simulate WebSocket disconnection during active chat.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ML_087</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" s="2" t="inlineStr"/>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify message list with corrupted/invalid message data</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Simulate receiving a message with missing or malformed fields.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>App should handle gracefully — skip or show placeholder. No crash.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ML_088</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Message List</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify message with exactly 1 character</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Send a single character 'a'.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message should display correctly in a properly sized bubble.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ML_089</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message with maximum allowed characters</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message should send and display correctly. May need 'Read more' expansion.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ML_090</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify message at character limit + 1</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_091</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify reaction with maximum number of unique reactions</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Add the maximum number of different reaction emojis to a single message.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ML_092</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr"/>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify message list with exactly 0 messages (new conversation)</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Open a brand new conversation with no messages.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Empty state should display. Composer should be ready for first message.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ML_093</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Message Types</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify short text message (1-50 chars)</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with 25 characters.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message should display in a compact bubble.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ML_094</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr"/>
-      <c r="C95" s="2" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify medium text message (51-500 chars)</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with 250 characters.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message should display in a medium-sized bubble with proper wrapping.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ML_095</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" s="2" t="inlineStr"/>
-      <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify long text message (501-5000 chars)</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with 2500 characters.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Message should display with 'Read more' or expandable view.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_096</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr"/>
-      <c r="C97" s="2" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify very long text message (5000+ chars)</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with 10000 characters.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Message should handle gracefully with expansion option. No performance issues.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ML_097</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr"/>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Media Sizes</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify small image (&lt;100KB)</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Send an image under 100KB.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Image should upload quickly and display as thumbnail.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ML_098</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr"/>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify medium image (100KB-5MB)</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Send an image of 2MB.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Image should upload with progress indicator and display correctly.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ML_099</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr"/>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify large image (5MB-25MB)</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Send an image of 15MB.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Image should upload with progress bar. May take longer. Should complete successfully.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ML_100</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr"/>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify oversized image (&gt;25MB or above limit)</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an image exceeding the file size limit.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Error message should display. File should not upload.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -820,119 +820,86 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>ML_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message List Display</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no messages in conversation</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty message list state</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a new conversation with no messages.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>ML_011</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message List Display</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no messages in conversation</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty message list state</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>ML_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify message list behavior without network</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Open a conversation.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cached messages should display or appropriate error message should show.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>ML_013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reactions</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify adding a reaction to a message</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Long press or hover on a message.
-2. Select a reaction emoji.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Reaction should appear below the message with count of 1.</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
@@ -940,69 +907,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ML_014</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify multiple reactions on a message</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Add different reactions from different users on the same message.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>All unique reactions should display below the message with respective counts.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ML_015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+          <t>ML_013</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Reactions</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify reaction count increments</t>
+          <t>Verify adding a reaction to a message</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Have multiple users react with the same emoji on a message.</t>
+          <t>1. Long press or hover on a message.
+2. Select a reaction emoji.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Reaction count should increment correctly (e.g., 👍 3).</t>
+          <t>Reaction should appear below the message with count of 1.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ML_016</t>
+          <t>ML_014</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -1010,17 +970,17 @@
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify removing own reaction</t>
+          <t>Verify multiple reactions on a message</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Tap on your own reaction on a message.</t>
+          <t>1. Add different reactions from different users on the same message.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Reaction should be removed. Count should decrement or reaction should disappear if count reaches 0.</t>
+          <t>All unique reactions should display below the message with respective counts.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1032,7 +992,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ML_017</t>
+          <t>ML_015</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1040,60 +1000,47 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify reaction details/list</t>
+          <t>Verify reaction count increments</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or click on a reaction below a message.</t>
+          <t>1. Have multiple users react with the same emoji on a message.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>List of users who reacted with that emoji should display.</t>
+          <t>Reaction count should increment correctly (e.g., 👍 3).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ML_018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reactions</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+          <t>ML_016</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify reaction fails without network</t>
+          <t>Verify removing own reaction</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to add a reaction.</t>
+          <t>1. Tap on your own reaction on a message.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Error message should display or reaction should queue for retry.</t>
+          <t>Reaction should be removed. Count should decrement or reaction should disappear if count reaches 0.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1105,101 +1052,78 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ML_019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reply</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_017</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify reply option available on message</t>
+          <t>Verify reaction details/list</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a message.
-2. Observe message menu.</t>
+          <t>1. Long press or click on a reaction below a message.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Reply option should be available in the message action menu.</t>
+          <t>List of users who reacted with that emoji should display.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ML_020</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify reply shows original message preview</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Select reply on a message.
-2. Observe composer area.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Original message preview should appear above the input field with close button.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ML_021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
+          <t>ML_018</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Verify Reactions</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify sending a reply message</t>
+          <t>Verify reaction fails without network</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Select reply on a message.
-2. Type reply text.
-3. Send.</t>
+          <t>1. Disconnect network.
+2. Try to add a reaction.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Reply should appear in chat with reference to the original message (quoted).</t>
+          <t>Error message should display or reaction should queue for retry.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1209,101 +1133,81 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>ML_022</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify tapping on replied message scrolls to original</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Tap on the quoted/original message in a reply bubble.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Chat should scroll to the original message and highlight it briefly.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ML_023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
+          <t>ML_019</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Verify Reply</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel reply</t>
+          <t>Verify reply option available on message</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Select reply on a message.
-2. Click close/cancel on the reply preview.</t>
+          <t>1. Long press or hover on a message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reply preview should dismiss and composer should return to normal state.</t>
+          <t>Reply option should be available in the message action menu.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ML_024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reply In Thread</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_020</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Reply In Thread' option in message menu</t>
+          <t>Verify reply shows original message preview</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a message.
-2. Observe message menu.</t>
+          <t>1. Select reply on a message.
+2. Observe composer area.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>'Reply In Thread' option should be available.</t>
+          <t>Original message preview should appear above the input field with close button.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1315,7 +1219,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ML_025</t>
+          <t>ML_021</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1323,17 +1227,19 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify thread panel opens on 'Reply In Thread'</t>
+          <t>Verify sending a reply message</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Reply In Thread' on a message.</t>
+          <t>1. Select reply on a message.
+2. Type reply text.
+3. Send.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Thread panel should open showing the original message and thread replies.</t>
+          <t>Reply should appear in chat with reference to the original message (quoted).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1345,7 +1251,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ML_026</t>
+          <t>ML_022</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -1353,30 +1259,29 @@
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify thread reply count on parent message</t>
+          <t>Verify tapping on replied message scrolls to original</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Reply in a thread.
-2. Go back to main chat.</t>
+          <t>1. Tap on the quoted/original message in a reply bubble.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Parent message should show thread reply count (e.g., '3 replies').</t>
+          <t>Chat should scroll to the original message and highlight it briefly.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ML_027</t>
+          <t>ML_023</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -1384,29 +1289,30 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking thread count opens thread</t>
+          <t>Verify cancel reply</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Click on thread reply count on a parent message.</t>
+          <t>1. Select reply on a message.
+2. Click close/cancel on the reply preview.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Thread panel should open with all thread replies.</t>
+          <t>Reply preview should dismiss and composer should return to normal state.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ML_028</t>
+          <t>ML_024</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1416,7 +1322,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Verify Copy Message</t>
+          <t>Verify Reply In Thread</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1426,18 +1332,18 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Copy' option in message menu</t>
+          <t>Verify 'Reply In Thread' option in message menu</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a text message.
+          <t>1. Long press or hover on a message.
 2. Observe message menu.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>'Copy' option should be available.</t>
+          <t>'Reply In Thread' option should be available.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1449,7 +1355,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ML_029</t>
+          <t>ML_025</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1457,18 +1363,17 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify copying text message</t>
+          <t>Verify thread panel opens on 'Reply In Thread'</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Copy' on a text message.
-2. Paste in input field.</t>
+          <t>1. Click 'Reply In Thread' on a message.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Message text should be copied to clipboard and paste correctly.</t>
+          <t>Thread panel should open showing the original message and thread replies.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1480,112 +1385,99 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ML_030</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Verify Copy Message</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify copy not available for media-only messages</t>
+          <t>Verify thread reply count on parent message</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on an image/video message with no caption.</t>
+          <t>1. Reply in a thread.
+2. Go back to main chat.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
+          <t>Parent message should show thread reply count (e.g., '3 replies').</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ML_031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Verify Edit Message</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_027</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Edit' option for own messages</t>
+          <t>Verify clicking thread count opens thread</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on own sent text message.
-2. Observe message menu.</t>
+          <t>1. Click on thread reply count on a parent message.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>'Edit' option should be available for own messages only.</t>
+          <t>Thread panel should open with all thread replies.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ML_032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
+          <t>ML_028</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Verify Copy Message</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a message</t>
+          <t>Verify 'Copy' option in message menu</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Edit' on own message.
-2. Modify text.
-3. Save/Send.</t>
+          <t>1. Long press or hover on a text message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Message should update with new text and show 'edited' indicator.</t>
+          <t>'Copy' option should be available.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1597,7 +1489,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ML_033</t>
+          <t>ML_029</t>
         </is>
       </c>
       <c r="B34" s="2" t="n"/>
@@ -1605,83 +1497,50 @@
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel edit</t>
+          <t>Verify copying text message</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Edit' on own message.
-2. Click cancel.</t>
+          <t>1. Click 'Copy' on a text message.
+2. Paste in input field.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Edit mode should dismiss and original message should remain unchanged.</t>
+          <t>Message text should be copied to clipboard and paste correctly.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ML_034</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Verify Edit Message</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Verify 'Edit' not available for others' messages</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>'Edit' option should NOT appear for messages sent by other users.</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ML_035</t>
+          <t>ML_030</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Verify Message Info</t>
+          <t>Verify Copy Message</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1691,121 +1550,102 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Info' option in message menu</t>
+          <t>Verify copy not available for media-only messages</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on own message.
-2. Observe message menu.</t>
+          <t>1. Long press on an image/video message with no caption.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>'Info' option should be available.</t>
+          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ML_036</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Verify message info shows delivery details</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Click 'Info' on own message.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Message info panel should show sent time, delivered time, and read time.</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ML_037</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
+          <t>ML_031</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Verify Edit Message</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify message info in group shows read/delivered by</t>
+          <t>Verify 'Edit' option for own messages</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Info' on own message in a group chat.</t>
+          <t>1. Long press or hover on own sent text message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Info should show list of members with delivered and read status for each.</t>
+          <t>'Edit' option should be available for own messages only.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ML_038</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Message</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_032</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Delete' option for own messages</t>
+          <t>Verify editing a message</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on own message.
-2. Observe message menu.</t>
+          <t>1. Click 'Edit' on own message.
+2. Modify text.
+3. Save/Send.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>'Delete' option should be available for own messages.</t>
+          <t>Message should update with new text and show 'edited' indicator.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1817,7 +1657,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ML_039</t>
+          <t>ML_033</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -1825,155 +1665,124 @@
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify delete confirmation dialog</t>
+          <t>Verify cancel edit</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Delete' on own message.</t>
+          <t>1. Click 'Edit' on own message.
+2. Click cancel.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear asking to confirm deletion.</t>
+          <t>Edit mode should dismiss and original message should remain unchanged.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ML_040</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Verify message deleted on confirm</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Click confirm in delete dialog.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Message should be removed or replaced with 'This message was deleted' text.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ML_041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
+          <t>ML_034</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Verify Edit Message</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel delete keeps message</t>
+          <t>Verify 'Edit' not available for others' messages</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1. Click cancel in delete dialog.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Message should remain unchanged in the chat.</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>ML_042</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Message</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Verify 'Delete' not available for others' messages</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>'Edit' option should NOT appear for messages sent by other users.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ML_043</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
+          <t>ML_035</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message Info</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify delete fails without network</t>
+          <t>Verify 'Info' option in message menu</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to delete a message.</t>
+          <t>1. Long press or hover on own message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Error message should display indicating network issue.</t>
+          <t>'Info' option should be available.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1985,38 +1794,25 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ML_044</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Verify Notifications</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and app is in background</t>
-        </is>
-      </c>
+          <t>ML_036</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify push notification for new message</t>
+          <t>Verify message info shows delivery details</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message from another user.
-2. Observe notification on device.</t>
+          <t>1. Click 'Info' on own message.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Push notification should appear with sender name and message preview.</t>
+          <t>Message info panel should show sent time, delivered time, and read time.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2028,7 +1824,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ML_045</t>
+          <t>ML_037</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -2036,139 +1832,120 @@
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify notification tap opens correct conversation</t>
+          <t>Verify message info in group shows read/delivered by</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a notification.
-2. Tap on it.</t>
+          <t>1. Click 'Info' on own message in a group chat.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>App should open and navigate to the correct conversation with the new message.</t>
+          <t>Info should show list of members with delivered and read status for each.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ML_046</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
+          <t>ML_038</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Message</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open in foreground</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify in-app notification for message in different chat</t>
+          <t>Verify 'Delete' option for own messages</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Be in conversation A.
-2. Receive message in conversation B.</t>
+          <t>1. Long press or hover on own message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>In-app notification/banner should appear for the new message in conversation B.</t>
+          <t>'Delete' option should be available for own messages.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ML_047</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Verify Notifications</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>User has notifications disabled</t>
-        </is>
-      </c>
+          <t>ML_039</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify no notification when disabled</t>
+          <t>Verify delete confirmation dialog</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Disable notifications in settings.
-2. Receive a message.</t>
+          <t>1. Click 'Delete' on own message.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>No push notification should appear.</t>
+          <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ML_048</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Verify Calling from Message List</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
+          <t>ML_040</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call button in chat header</t>
+          <t>Verify message deleted on confirm</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Open a one-on-one conversation.
-2. Observe chat header.</t>
+          <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Audio call icon should be visible in the chat header.</t>
+          <t>Message should be removed or replaced with 'This message was deleted' text.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2180,7 +1957,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ML_049</t>
+          <t>ML_041</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -2188,78 +1965,70 @@
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify video call button in chat header</t>
+          <t>Verify cancel delete keeps message</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Open a one-on-one conversation.
-2. Observe chat header.</t>
+          <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Video call icon should be visible in the chat header.</t>
+          <t>Message should remain unchanged in the chat.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>ML_050</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Verify initiating audio call from chat</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>1. Click audio call icon in chat header.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Audio call should initiate with the user. Call screen should appear.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ML_051</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
+          <t>ML_042</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Message</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify initiating video call from chat</t>
+          <t>Verify 'Delete' not available for others' messages</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Click video call icon in chat header.</t>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Video call should initiate with the user. Video call screen should appear.</t>
+          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2271,30 +2040,30 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ML_052</t>
+          <t>ML_043</t>
         </is>
       </c>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify group call button in group chat header</t>
+          <t>Verify delete fails without network</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1. Open a group conversation.
-2. Observe chat header.</t>
+          <t>1. Disconnect network.
+2. Try to delete a message.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Group call icon should be visible in the group chat header.</t>
+          <t>Error message should display indicating network issue.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2304,83 +2073,62 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ML_053</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group Actions in Message List</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Verify group info accessible from chat header</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group conversation.
-2. Click on group name or info icon in header.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Group info panel should open showing group details, members, and actions.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ML_054</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
+          <t>ML_044</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Verify Notifications</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and app is in background</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify member join/leave messages in chat</t>
+          <t>Verify push notification for new message</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. Have a member join or leave the group.
-2. Observe message list.</t>
+          <t>1. Send a message from another user.
+2. Observe notification on device.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>System message should appear (e.g., 'John joined the group', 'Jane left the group').</t>
+          <t>Push notification should appear with sender name and message preview.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ML_055</t>
+          <t>ML_045</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -2388,185 +2136,159 @@
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify admin action messages in chat</t>
+          <t>Verify notification tap opens correct conversation</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Admin kicks/bans a member or changes scope.
-2. Observe message list.</t>
+          <t>1. Receive a notification.
+2. Tap on it.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>System message should appear reflecting the admin action.</t>
+          <t>App should open and navigate to the correct conversation with the new message.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ML_056</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message Types Display</t>
-        </is>
-      </c>
+          <t>ML_046</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and chat is open in foreground</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify text message display</t>
+          <t>Verify in-app notification for message in different chat</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. Send/receive a text message.
-2. Observe in message list.</t>
+          <t>1. Be in conversation A.
+2. Receive message in conversation B.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Text message should display in a message bubble with proper formatting.</t>
+          <t>In-app notification/banner should appear for the new message in conversation B.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>ML_057</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="n"/>
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Verify image message display</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive an image.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Image should display as thumbnail in chat. Tapping should open full-size preview.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ML_058</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
+          <t>ML_047</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Verify Notifications</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>User has notifications disabled</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify video message display</t>
+          <t>Verify no notification when disabled</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Send/receive a video.
-2. Observe in message list.</t>
+          <t>1. Disable notifications in settings.
+2. Receive a message.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Video thumbnail with play icon should display. Tapping should play the video.</t>
+          <t>No push notification should appear.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>ML_059</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message display</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive an audio message.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Audio player with play/pause button and duration should display.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ML_060</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
+          <t>ML_048</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Verify Calling from Message List</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify document/file message display</t>
+          <t>Verify audio call button in chat header</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1. Send/receive a document.
-2. Observe in message list.</t>
+          <t>1. Open a one-on-one conversation.
+2. Observe chat header.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>File icon with file name and size should display. Tapping should download/open.</t>
+          <t>Audio call icon should be visible in the chat header.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2578,7 +2300,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ML_061</t>
+          <t>ML_049</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -2586,30 +2308,30 @@
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify link preview in message</t>
+          <t>Verify video call button in chat header</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message containing a URL.
-2. Observe in message list.</t>
+          <t>1. Open a one-on-one conversation.
+2. Observe chat header.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Link preview with title, description, and thumbnail should display below the message.</t>
+          <t>Video call icon should be visible in the chat header.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ML_062</t>
+          <t>ML_050</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -2617,30 +2339,29 @@
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker message display</t>
+          <t>Verify initiating audio call from chat</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Send/receive a sticker.
-2. Observe in message list.</t>
+          <t>1. Click audio call icon in chat header.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Sticker should display as a larger image without message bubble.</t>
+          <t>Audio call should initiate with the user. Call screen should appear.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ML_063</t>
+          <t>ML_051</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -2648,21 +2369,420 @@
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
+          <t>Verify initiating video call from chat</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Click video call icon in chat header.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Video call should initiate with the user. Video call screen should appear.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ML_052</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify group call button in group chat header</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a group conversation.
+2. Observe chat header.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Group call icon should be visible in the group chat header.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ML_053</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group Actions in Message List</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify group info accessible from chat header</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a group conversation.
+2. Click on group name or info icon in header.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Group info panel should open showing group details, members, and actions.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ML_054</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify member join/leave messages in chat</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Have a member join or leave the group.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>System message should appear (e.g., 'John joined the group', 'Jane left the group').</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ML_055</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Verify admin action messages in chat</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Admin kicks/bans a member or changes scope.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>System message should appear reflecting the admin action.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ML_056</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message Types Display</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Verify text message display</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive a text message.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Text message should display in a message bubble with proper formatting.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ML_057</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Verify image message display</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive an image.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Image should display as thumbnail in chat. Tapping should open full-size preview.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ML_058</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Verify video message display</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive a video.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Video thumbnail with play icon should display. Tapping should play the video.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ML_059</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio message display</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive an audio message.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Audio player with play/pause button and duration should display.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ML_060</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify document/file message display</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive a document.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>File icon with file name and size should display. Tapping should download/open.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ML_061</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify link preview in message</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing a URL.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Link preview with title, description, and thumbnail should display below the message.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ML_062</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify sticker message display</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive a sticker.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Sticker should display as a larger image without message bubble.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ML_063</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>Verify emoji-only message display</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with only emojis (1-3).
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Emojis should display in larger size without message bubble background.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
@@ -3198,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3328,66 +3448,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ML_077</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Security: Message List</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify XSS prevention in message display</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
 2. Observe in receiver's message list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ML_078</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify SQL injection prevention in messages</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Message should display as plain text. No database errors or data loss.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -3399,7 +3499,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ML_079</t>
+          <t>ML_078</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -3407,21 +3507,51 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Verify SQL injection prevention in messages</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Message should display as plain text. No database errors or data loss.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ML_079</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Verify message with malicious URL</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Send a message with a phishing/malicious URL.
 2. Observe link preview.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Link should be clickable but app should warn about external links or have URL validation.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
@@ -3439,7 +3569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3689,68 +3819,78 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ML_086</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Edge Case: Message List</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify message list when WebSocket disconnects</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Simulate WebSocket disconnection during active chat.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ML_087</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+          <t>ML_086</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Verify message list when WebSocket disconnects</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate WebSocket disconnection during active chat.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ML_087</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Verify message list with corrupted/invalid message data</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Simulate receiving a message with missing or malformed fields.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>App should handle gracefully — skip or show placeholder. No crash.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -3997,7 +4137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4279,34 +4419,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>ML_100</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ML_100</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify oversized image (&gt;25MB or above limit)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an image exceeding the file size limit.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Error message should display. File should not upload.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -820,167 +820,203 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ML_013</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Verify Reactions</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding a reaction to a message</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press or hover on a message.
+2. Select a reaction emoji.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Reaction should appear below the message with count of 1.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ML_011</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message List Display</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no messages in conversation</t>
-        </is>
-      </c>
+          <t>ML_014</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify empty message list state</t>
+          <t>Verify multiple reactions on a message</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Open a new conversation with no messages.</t>
+          <t>1. Add different reactions from different users on the same message.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+          <t>All unique reactions should display below the message with respective counts.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ML_012</t>
+          <t>ML_015</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify message list behavior without network</t>
+          <t>Verify reaction count increments</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Open a conversation.</t>
+          <t>1. Have multiple users react with the same emoji on a message.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Cached messages should display or appropriate error message should show.</t>
+          <t>Reaction count should increment correctly (e.g., 👍 3).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ML_016</t>
+        </is>
+      </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify removing own reaction</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Tap on your own reaction on a message.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Reaction should be removed. Count should decrement or reaction should disappear if count reaches 0.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ML_013</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reactions</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_017</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a reaction to a message</t>
+          <t>Verify reaction details/list</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a message.
-2. Select a reaction emoji.</t>
+          <t>1. Long press or click on a reaction below a message.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Reaction should appear below the message with count of 1.</t>
+          <t>List of users who reacted with that emoji should display.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ML_014</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+          <t>ML_019</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Verify Reply</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple reactions on a message</t>
+          <t>Verify reply option available on message</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Add different reactions from different users on the same message.</t>
+          <t>1. Long press or hover on a message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>All unique reactions should display below the message with respective counts.</t>
+          <t>Reply option should be available in the message action menu.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -992,7 +1028,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ML_015</t>
+          <t>ML_020</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1000,29 +1036,30 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify reaction count increments</t>
+          <t>Verify reply shows original message preview</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Have multiple users react with the same emoji on a message.</t>
+          <t>1. Select reply on a message.
+2. Observe composer area.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Reaction count should increment correctly (e.g., 👍 3).</t>
+          <t>Original message preview should appear above the input field with close button.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ML_016</t>
+          <t>ML_021</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1030,17 +1067,19 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify removing own reaction</t>
+          <t>Verify sending a reply message</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Tap on your own reaction on a message.</t>
+          <t>1. Select reply on a message.
+2. Type reply text.
+3. Send.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Reaction should be removed. Count should decrement or reaction should disappear if count reaches 0.</t>
+          <t>Reply should appear in chat with reference to the original message (quoted).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1052,7 +1091,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ML_017</t>
+          <t>ML_022</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1060,17 +1099,17 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify reaction details/list</t>
+          <t>Verify tapping on replied message scrolls to original</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or click on a reaction below a message.</t>
+          <t>1. Tap on the quoted/original message in a reply bubble.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>List of users who reacted with that emoji should display.</t>
+          <t>Chat should scroll to the original message and highlight it briefly.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1080,50 +1119,71 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ML_023</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Verify cancel reply</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Select reply on a message.
+2. Click close/cancel on the reply preview.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Reply preview should dismiss and composer should return to normal state.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ML_018</t>
+          <t>ML_024</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify Reactions</t>
+          <t>Verify Reply In Thread</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify reaction fails without network</t>
+          <t>Verify 'Reply In Thread' option in message menu</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to add a reaction.</t>
+          <t>1. Long press or hover on a message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Error message should display or reaction should queue for retry.</t>
+          <t>'Reply In Thread' option should be available.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1133,50 +1193,58 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ML_025</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread panel opens on 'Reply In Thread'</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'Reply In Thread' on a message.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Thread panel should open showing the original message and thread replies.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ML_019</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reply</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify reply option available on message</t>
+          <t>Verify thread reply count on parent message</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a message.
-2. Observe message menu.</t>
+          <t>1. Reply in a thread.
+2. Go back to main chat.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reply option should be available in the message action menu.</t>
+          <t>Parent message should show thread reply count (e.g., '3 replies').</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1188,7 +1256,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ML_020</t>
+          <t>ML_027</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -1196,50 +1264,60 @@
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify reply shows original message preview</t>
+          <t>Verify clicking thread count opens thread</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Select reply on a message.
-2. Observe composer area.</t>
+          <t>1. Click on thread reply count on a parent message.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Original message preview should appear above the input field with close button.</t>
+          <t>Thread panel should open with all thread replies.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ML_021</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
+          <t>ML_028</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Copy Message</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify sending a reply message</t>
+          <t>Verify 'Copy' option in message menu</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Select reply on a message.
-2. Type reply text.
-3. Send.</t>
+          <t>1. Long press or hover on a text message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Reply should appear in chat with reference to the original message (quoted).</t>
+          <t>'Copy' option should be available.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1251,7 +1329,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ML_022</t>
+          <t>ML_029</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -1259,91 +1337,93 @@
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify tapping on replied message scrolls to original</t>
+          <t>Verify copying text message</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Tap on the quoted/original message in a reply bubble.</t>
+          <t>1. Click 'Copy' on a text message.
+2. Paste in input field.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Chat should scroll to the original message and highlight it briefly.</t>
+          <t>Message text should be copied to clipboard and paste correctly.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ML_023</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
+          <t>ML_031</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Verify Edit Message</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel reply</t>
+          <t>Verify 'Edit' option for own messages</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Select reply on a message.
-2. Click close/cancel on the reply preview.</t>
+          <t>1. Long press or hover on own sent text message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Reply preview should dismiss and composer should return to normal state.</t>
+          <t>'Edit' option should be available for own messages only.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ML_024</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Verify Reply In Thread</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_032</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Reply In Thread' option in message menu</t>
+          <t>Verify editing a message</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a message.
-2. Observe message menu.</t>
+          <t>1. Click 'Edit' on own message.
+2. Modify text.
+3. Save/Send.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>'Reply In Thread' option should be available.</t>
+          <t>Message should update with new text and show 'edited' indicator.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1355,7 +1435,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ML_025</t>
+          <t>ML_033</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1363,48 +1443,61 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify thread panel opens on 'Reply In Thread'</t>
+          <t>Verify cancel edit</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Reply In Thread' on a message.</t>
+          <t>1. Click 'Edit' on own message.
+2. Click cancel.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Thread panel should open showing the original message and thread replies.</t>
+          <t>Edit mode should dismiss and original message should remain unchanged.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ML_026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
+          <t>ML_035</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message Info</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify thread reply count on parent message</t>
+          <t>Verify 'Info' option in message menu</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Reply in a thread.
-2. Go back to main chat.</t>
+          <t>1. Long press or hover on own message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Parent message should show thread reply count (e.g., '3 replies').</t>
+          <t>'Info' option should be available.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1416,7 +1509,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ML_027</t>
+          <t>ML_036</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
@@ -1424,91 +1517,90 @@
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking thread count opens thread</t>
+          <t>Verify message info shows delivery details</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Click on thread reply count on a parent message.</t>
+          <t>1. Click 'Info' on own message.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Thread panel should open with all thread replies.</t>
+          <t>Message info panel should show sent time, delivered time, and read time.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ML_028</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Verify Copy Message</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_037</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Copy' option in message menu</t>
+          <t>Verify message info in group shows read/delivered by</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on a text message.
-2. Observe message menu.</t>
+          <t>1. Click 'Info' on own message in a group chat.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>'Copy' option should be available.</t>
+          <t>Info should show list of members with delivered and read status for each.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ML_029</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
+          <t>ML_038</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Message</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify copying text message</t>
+          <t>Verify 'Delete' option for own messages</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Copy' on a text message.
-2. Paste in input field.</t>
+          <t>1. Long press or hover on own message.
+2. Observe message menu.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Message text should be copied to clipboard and paste correctly.</t>
+          <t>'Delete' option should be available for own messages.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1518,71 +1610,99 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ML_039</t>
+        </is>
+      </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verify delete confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'Delete' on own message.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog should appear asking to confirm deletion.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ML_030</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Verify Copy Message</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_040</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify copy not available for media-only messages</t>
+          <t>Verify message deleted on confirm</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on an image/video message with no caption.</t>
+          <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
+          <t>Message should be removed or replaced with 'This message was deleted' text.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ML_041</t>
+        </is>
+      </c>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify cancel delete keeps message</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Click cancel in delete dialog.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Message should remain unchanged in the chat.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ML_031</t>
+          <t>ML_044</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1592,28 +1712,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Verify Edit Message</t>
+          <t>Verify Notifications</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and app is in background</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Edit' option for own messages</t>
+          <t>Verify push notification for new message</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on own sent text message.
-2. Observe message menu.</t>
+          <t>1. Send a message from another user.
+2. Observe notification on device.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>'Edit' option should be available for own messages only.</t>
+          <t>Push notification should appear with sender name and message preview.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1625,7 +1745,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ML_032</t>
+          <t>ML_045</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -1633,19 +1753,18 @@
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a message</t>
+          <t>Verify notification tap opens correct conversation</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Edit' on own message.
-2. Modify text.
-3. Save/Send.</t>
+          <t>1. Receive a notification.
+2. Tap on it.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Message should update with new text and show 'edited' indicator.</t>
+          <t>App should open and navigate to the correct conversation with the new message.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1657,26 +1776,30 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ML_033</t>
+          <t>ML_046</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open in foreground</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel edit</t>
+          <t>Verify in-app notification for message in different chat</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Edit' on own message.
-2. Click cancel.</t>
+          <t>1. Be in conversation A.
+2. Receive message in conversation B.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Edit mode should dismiss and original message should remain unchanged.</t>
+          <t>In-app notification/banner should appear for the new message in conversation B.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1686,50 +1809,71 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ML_048</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Verify Calling from Message List</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call button in chat header</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a one-on-one conversation.
+2. Observe chat header.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Audio call icon should be visible in the chat header.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ML_034</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Verify Edit Message</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_049</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Edit' not available for others' messages</t>
+          <t>Verify video call button in chat header</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
+          <t>1. Open a one-on-one conversation.
+2. Observe chat header.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>'Edit' option should NOT appear for messages sent by other users.</t>
+          <t>Video call icon should be visible in the chat header.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1739,50 +1883,57 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ML_050</t>
+        </is>
+      </c>
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify initiating audio call from chat</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Click audio call icon in chat header.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Audio call should initiate with the user. Call screen should appear.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ML_035</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message Info</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_051</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Info' option in message menu</t>
+          <t>Verify initiating video call from chat</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on own message.
-2. Observe message menu.</t>
+          <t>1. Click video call icon in chat header.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>'Info' option should be available.</t>
+          <t>Video call should initiate with the user. Video call screen should appear.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1794,25 +1945,30 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ML_036</t>
+          <t>ML_052</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify message info shows delivery details</t>
+          <t>Verify group call button in group chat header</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Info' on own message.</t>
+          <t>1. Open a group conversation.
+2. Observe chat header.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Message info panel should show sent time, delivered time, and read time.</t>
+          <t>Group call icon should be visible in the group chat header.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1824,80 +1980,81 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ML_037</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
+          <t>ML_053</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group Actions in Message List</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify message info in group shows read/delivered by</t>
+          <t>Verify group info accessible from chat header</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Info' on own message in a group chat.</t>
+          <t>1. Open a group conversation.
+2. Click on group name or info icon in header.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Info should show list of members with delivered and read status for each.</t>
+          <t>Group info panel should open showing group details, members, and actions.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ML_038</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Message</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_054</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Delete' option for own messages</t>
+          <t>Verify member join/leave messages in chat</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Long press or hover on own message.
-2. Observe message menu.</t>
+          <t>1. Have a member join or leave the group.
+2. Observe message list.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>'Delete' option should be available for own messages.</t>
+          <t>System message should appear (e.g., 'John joined the group', 'Jane left the group').</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ML_039</t>
+          <t>ML_055</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -1905,47 +2062,61 @@
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify delete confirmation dialog</t>
+          <t>Verify admin action messages in chat</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Delete' on own message.</t>
+          <t>1. Admin kicks/bans a member or changes scope.
+2. Observe message list.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear asking to confirm deletion.</t>
+          <t>System message should appear reflecting the admin action.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ML_040</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
+          <t>ML_056</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message Types Display</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify message deleted on confirm</t>
+          <t>Verify text message display</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Click confirm in delete dialog.</t>
+          <t>1. Send/receive a text message.
+2. Observe in message list.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Message should be removed or replaced with 'This message was deleted' text.</t>
+          <t>Text message should display in a message bubble with proper formatting.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -1957,7 +2128,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ML_041</t>
+          <t>ML_057</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -1965,70 +2136,80 @@
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel delete keeps message</t>
+          <t>Verify image message display</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Click cancel in delete dialog.</t>
+          <t>1. Send/receive an image.
+2. Observe in message list.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Message should remain unchanged in the chat.</t>
+          <t>Image should display as thumbnail in chat. Tapping should open full-size preview.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ML_058</t>
+        </is>
+      </c>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify video message display</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Send/receive a video.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Video thumbnail with play icon should display. Tapping should play the video.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ML_042</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Message</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>ML_059</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Delete' not available for others' messages</t>
+          <t>Verify audio message display</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
+          <t>1. Send/receive an audio message.
+2. Observe in message list.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
+          <t>Audio player with play/pause button and duration should display.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2040,30 +2221,26 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ML_043</t>
+          <t>ML_060</t>
         </is>
       </c>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify delete fails without network</t>
+          <t>Verify document/file message display</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to delete a message.</t>
+          <t>1. Send/receive a document.
+2. Observe in message list.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Error message should display indicating network issue.</t>
+          <t>File icon with file name and size should display. Tapping should download/open.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2073,62 +2250,71 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ML_061</t>
+        </is>
+      </c>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify link preview in message</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing a URL.
+2. Observe in message list.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Link preview with title, description, and thumbnail should display below the message.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ML_044</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Verify Notifications</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and app is in background</t>
-        </is>
-      </c>
+          <t>ML_062</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify push notification for new message</t>
+          <t>Verify sticker message display</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message from another user.
-2. Observe notification on device.</t>
+          <t>1. Send/receive a sticker.
+2. Observe in message list.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Push notification should appear with sender name and message preview.</t>
+          <t>Sticker should display as a larger image without message bubble.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ML_045</t>
+          <t>ML_063</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -2136,655 +2322,359 @@
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify notification tap opens correct conversation</t>
+          <t>Verify emoji-only message display</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a notification.
-2. Tap on it.</t>
+          <t>1. Send a message with only emojis (1-3).
+2. Observe in message list.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>App should open and navigate to the correct conversation with the new message.</t>
+          <t>Emojis should display in larger size without message bubble background.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>ML_046</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open in foreground</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Verify in-app notification for message in different chat</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>1. Be in conversation A.
-2. Receive message in conversation B.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>In-app notification/banner should appear for the new message in conversation B.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ML_011</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message List Display</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no messages in conversation</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty message list state</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>ML_012</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list behavior without network</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Open a conversation.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Cached messages should display or appropriate error message should show.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ML_018</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Verify Reactions</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Verify reaction fails without network</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to add a reaction.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or reaction should queue for retry.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ML_030</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Verify Copy Message</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify copy not available for media-only messages</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on an image/video message with no caption.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ML_034</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Verify Edit Message</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Edit' not available for others' messages</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>'Edit' option should NOT appear for messages sent by other users.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ML_042</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Message</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Delete' not available for others' messages</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ML_043</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify delete fails without network</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to delete a message.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display indicating network issue.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>ML_047</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Verify Notifications</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>User has notifications disabled</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Verify no notification when disabled</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Disable notifications in settings.
 2. Receive a message.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>No push notification should appear.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>ML_048</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Verify Calling from Message List</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call button in chat header</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a one-on-one conversation.
-2. Observe chat header.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Audio call icon should be visible in the chat header.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>ML_049</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Verify video call button in chat header</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a one-on-one conversation.
-2. Observe chat header.</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Video call icon should be visible in the chat header.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>ML_050</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Verify initiating audio call from chat</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>1. Click audio call icon in chat header.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Audio call should initiate with the user. Call screen should appear.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>ML_051</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Verify initiating video call from chat</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Click video call icon in chat header.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Video call should initiate with the user. Video call screen should appear.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>ML_052</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Verify group call button in group chat header</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group conversation.
-2. Observe chat header.</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Group call icon should be visible in the group chat header.</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>ML_053</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group Actions in Message List</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Verify group info accessible from chat header</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group conversation.
-2. Click on group name or info icon in header.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Group info panel should open showing group details, members, and actions.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>ML_054</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Verify member join/leave messages in chat</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1. Have a member join or leave the group.
-2. Observe message list.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>System message should appear (e.g., 'John joined the group', 'Jane left the group').</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>ML_055</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Verify admin action messages in chat</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>1. Admin kicks/bans a member or changes scope.
-2. Observe message list.</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>System message should appear reflecting the admin action.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>ML_056</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message Types Display</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Verify text message display</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive a text message.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Text message should display in a message bubble with proper formatting.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>ML_057</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Verify image message display</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive an image.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Image should display as thumbnail in chat. Tapping should open full-size preview.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>ML_058</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Verify video message display</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive a video.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Video thumbnail with play icon should display. Tapping should play the video.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>ML_059</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message display</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive an audio message.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Audio player with play/pause button and duration should display.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>ML_060</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Verify document/file message display</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive a document.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>File icon with file name and size should display. Tapping should download/open.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>ML_061</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Verify link preview in message</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message containing a URL.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Link preview with title, description, and thumbnail should display below the message.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>ML_062</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Verify sticker message display</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive a sticker.
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Sticker should display as a larger image without message bubble.</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>ML_063</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Verify emoji-only message display</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message with only emojis (1-3).
-2. Observe in message list.</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Emojis should display in larger size without message bubble background.</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
         </is>
       </c>
     </row>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,2238 +465,3905 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Message List Display</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify message list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Open any conversation.
 2. Observe message list area.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Messages should load and display in chronological order with sender info and timestamps.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify sender message alignment (right side)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Observe sent messages.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Sender's messages should appear on the right side of the chat.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ML_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify receiver message alignment (left side)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Observe received messages.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Receiver's messages should appear on the left side of the chat.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ML_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify user name displayed above messages</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Observe messages from different users.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Sender's name should display above their message bubble in group chats.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ML_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify user avatar displayed next to messages</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Observe avatars next to messages.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Sender's avatar/profile picture should display next to their messages.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ML_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify message timestamp display</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Observe timestamps on messages.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Each message should display time in readable format (e.g., '02:35 PM').</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>ML_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify date separator between different days</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation with messages spanning multiple days.
 2. Observe date separators.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Date separator (e.g., 'Today', 'Yesterday', 'Feb 15, 2025') should appear between messages of different days.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ML_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify scroll to load older messages</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation with many messages.
 2. Scroll up to the top.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Older messages should load as user scrolls up. Loading indicator should appear during fetch.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ML_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify auto-scroll to latest message on open</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation with many messages.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Chat should auto-scroll to the most recent message at the bottom.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ML_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify new incoming message auto-scrolls</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Be at the bottom of a conversation.
 2. Receive a new message.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Chat should auto-scroll to show the new incoming message.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>ML_013</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Verify Reactions</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify adding a reaction to a message</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on a message.
 2. Select a reaction emoji.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Reaction should appear below the message with count of 1.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>ML_014</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify multiple reactions on a message</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Add different reactions from different users on the same message.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>All unique reactions should display below the message with respective counts.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ML_015</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify reaction count increments</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Have multiple users react with the same emoji on a message.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Reaction count should increment correctly (e.g., 👍 3).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ML_016</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify removing own reaction</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Tap on your own reaction on a message.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Reaction should be removed. Count should decrement or reaction should disappear if count reaches 0.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ML_017</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify reaction details/list</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Long press or click on a reaction below a message.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>List of users who reacted with that emoji should display.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>ML_019</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Verify Reply</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify reply option available on message</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on a message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Reply option should be available in the message action menu.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ML_020</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify reply shows original message preview</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Select reply on a message.
 2. Observe composer area.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Original message preview should appear above the input field with close button.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ML_021</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify sending a reply message</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Select reply on a message.
 2. Type reply text.
 3. Send.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Reply should appear in chat with reference to the original message (quoted).</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ML_022</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify tapping on replied message scrolls to original</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Tap on the quoted/original message in a reply bubble.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Chat should scroll to the original message and highlight it briefly.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>ML_023</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Verify cancel reply</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. Select reply on a message.
 2. Click close/cancel on the reply preview.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Reply preview should dismiss and composer should return to normal state.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>ML_024</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Verify Reply In Thread</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Verify 'Reply In Thread' option in message menu</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on a message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>'Reply In Thread' option should be available.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>ML_025</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Verify thread panel opens on 'Reply In Thread'</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Reply In Thread' on a message.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Thread panel should open showing the original message and thread replies.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>ML_026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Verify thread reply count on parent message</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. Reply in a thread.
 2. Go back to main chat.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Parent message should show thread reply count (e.g., '3 replies').</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>ML_027</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Verify clicking thread count opens thread</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. Click on thread reply count on a parent message.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Thread panel should open with all thread replies.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ML_028</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Verify Copy Message</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Verify 'Copy' option in message menu</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on a text message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>'Copy' option should be available.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>ML_029</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Verify copying text message</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Copy' on a text message.
 2. Paste in input field.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Message text should be copied to clipboard and paste correctly.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>ML_031</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Verify Edit Message</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Verify 'Edit' option for own messages</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on own sent text message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>'Edit' option should be available for own messages only.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>ML_032</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Verify editing a message</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Edit' on own message.
 2. Modify text.
 3. Save/Send.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Message should update with new text and show 'edited' indicator.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ML_033</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Verify cancel edit</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Edit' on own message.
 2. Click cancel.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Edit mode should dismiss and original message should remain unchanged.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>ML_035</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Verify Message Info</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Verify 'Info' option in message menu</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on own message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>'Info' option should be available.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>ML_036</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Verify message info shows delivery details</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Info' on own message.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Message info panel should show sent time, delivered time, and read time.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ML_037</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Verify message info in group shows read/delivered by</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Info' on own message in a group chat.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Info should show list of members with delivered and read status for each.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ML_038</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Message</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Verify 'Delete' option for own messages</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>1. Long press or hover on own message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>'Delete' option should be available for own messages.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>ML_039</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Verify delete confirmation dialog</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>1. Click 'Delete' on own message.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>ML_040</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Verify message deleted on confirm</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Message should be removed or replaced with 'This message was deleted' text.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>ML_041</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Verify cancel delete keeps message</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Message should remain unchanged in the chat.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ML_044</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Verify Notifications</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>User is logged in and app is in background</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Verify push notification for new message</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>1. Send a message from another user.
 2. Observe notification on device.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Push notification should appear with sender name and message preview.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>ML_045</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Verify notification tap opens correct conversation</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>1. Receive a notification.
 2. Tap on it.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>App should open and navigate to the correct conversation with the new message.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>ML_046</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open in foreground</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Verify in-app notification for message in different chat</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1. Be in conversation A.
 2. Receive message in conversation B.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>In-app notification/banner should appear for the new message in conversation B.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>ML_048</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Verify Calling from Message List</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Verify audio call button in chat header</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Observe chat header.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Audio call icon should be visible in the chat header.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>ML_049</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Verify video call button in chat header</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Observe chat header.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Video call icon should be visible in the chat header.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>ML_050</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Verify initiating audio call from chat</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>1. Click audio call icon in chat header.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Audio call should initiate with the user. Call screen should appear.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>ML_051</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Verify initiating video call from chat</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>1. Click video call icon in chat header.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Video call should initiate with the user. Video call screen should appear.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>ML_052</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Verify group call button in group chat header</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Observe chat header.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Group call icon should be visible in the group chat header.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>ML_053</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Verify Group Actions in Message List</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Verify group info accessible from chat header</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Click on group name or info icon in header.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>Group info panel should open showing group details, members, and actions.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>ML_054</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Verify member join/leave messages in chat</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>1. Have a member join or leave the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>System message should appear (e.g., 'John joined the group', 'Jane left the group').</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>ML_055</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Verify admin action messages in chat</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>1. Admin kicks/bans a member or changes scope.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>System message should appear reflecting the admin action.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>ML_056</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Verify Message Types Display</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Verify text message display</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>1. Send/receive a text message.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Text message should display in a message bubble with proper formatting.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ML_057</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Verify image message display</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>1. Send/receive an image.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Image should display as thumbnail in chat. Tapping should open full-size preview.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>ML_058</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Verify video message display</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>1. Send/receive a video.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Video thumbnail with play icon should display. Tapping should play the video.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>ML_059</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Verify audio message display</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>1. Send/receive an audio message.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Audio player with play/pause button and duration should display.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>ML_060</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Verify document/file message display</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>1. Send/receive a document.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>File icon with file name and size should display. Tapping should download/open.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>ML_061</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Verify link preview in message</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>1. Send a message containing a URL.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>Link preview with title, description, and thumbnail should display below the message.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>ML_062</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Verify sticker message display</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>1. Send/receive a sticker.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>Sticker should display as a larger image without message bubble.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>ML_063</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Verify emoji-only message display</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with only emojis (1-3).
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>Emojis should display in larger size without message bubble background.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>ML_011</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message List Display</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no messages in conversation</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty message list state</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a new conversation with no messages.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>ML_012</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Verify message list behavior without network</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Open a conversation.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>Cached messages should display or appropriate error message should show.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>ML_043</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Verify delete fails without network</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to delete a message.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Error message should display indicating network issue.</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>ML_101</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Message Translation</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>User logged in, translation enabled</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Verify translate message option appears in message actions</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat
+2. Long press/hover on message
+3. Check for translate option</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Translate option visible in message actions menu</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>ML_102</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Message Translation</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Message received in foreign language</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Verify message translates to user's language on click</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive foreign language message
+2. Click translate option</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Message translated text displayed below original</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>ML_103</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Message Forwarding</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>User logged in with messages</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Verify forward message option in actions menu</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat
+2. Hover on message
+3. Click forward option</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Forward dialog opens with user/group selection</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>ML_104</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Message Forwarding</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Forward dialog open</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Verify message forwards to selected user</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>1. Select target user
+2. Click forward/send</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Message forwarded successfully, confirmation shown</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ML_105</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Message Sharing</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>User logged in with messages</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Verify share message option in actions menu</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Click share option</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Share dialog/native share sheet opens</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ML_106</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Flag/Report Message</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>User logged in, flag option enabled</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Verify flag message option appears in actions</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check for flag option</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Flag message option visible in actions menu</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>ML_107</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Flag/Report Message</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Flag dialog open</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Verify user can flag message with remark</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>1. Click flag option
+2. Enter remark
+3. Submit</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Message flagged successfully, confirmation shown</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>ML_108</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Flag/Report Message</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>hideFlagRemarkField=false</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Verify remark text area visible in flag dialog</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>1. Click flag option
+2. Check for remark field</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Remark text area is visible and editable</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>ML_109</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Download Media</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Media message received (image/video/file)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Verify media message can be downloaded</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1. Click on media message
+2. Click download option</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Media file downloads to device</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>ML_110</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Message Privately</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>User in group chat</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Verify send message privately option in group</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1. Open group chat
+2. Hover on member's message
+3. Click message privately</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Private chat opens with that user</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>ML_111</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Message Privately</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>User in group chat</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Verify reply message privately option</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Click reply privately</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Private reply sent to user outside group</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>ML_112</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Mark as Unread</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>showMarkAsUnreadOption=true</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Verify mark as unread option appears</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat
+2. Hover on message
+3. Check for mark as unread</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Mark as unread option visible in actions</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>ML_113</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Mark as Unread</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Mark as unread option visible</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Verify marking message as unread works</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1. Click mark as unread
+2. Go back to conversation list</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Conversation shows unread indicator from that message</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>ML_114</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>showSmartReplies=true, incoming message with question</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Verify smart replies appear for incoming questions</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive message containing '?'
+2. Wait for smart replies delay</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Smart reply suggestions appear below message list</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>ML_115</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies visible</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Verify clicking smart reply sends message</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>1. Click on a smart reply suggestion</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Smart reply text sent as message</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>ML_116</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies Keywords</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>smartRepliesKeywords=['what','when','how']</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Verify smart replies trigger only for configured keywords</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive message with 'what'
+2. Receive message without keywords</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies appear only for keyword messages</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>ML_117</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Conversation Starters</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>showConversationStarters=true, new chat with no messages</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation starters appear in empty chat</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>1. Open new chat with no history</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Conversation starter suggestions displayed</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>ML_118</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Conversation Starters</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Starters visible</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Verify clicking starter sends message</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>1. Click on a conversation starter</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Starter text sent as message, chat begins</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>ML_119</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Moderation View</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>hideModerationView=false, moderated message exists</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Verify moderation status shown on messages</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message in moderated group
+2. Check message status</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Moderation status (pending/approved/disapproved) visible</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>ML_120</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Another user typing in chat</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing indicator appears</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>1. Other user starts typing
+2. Observe message list footer</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Typing indicator shown with user name</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>ML_121</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>User stops typing</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing indicator disappears</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>1. Other user stops typing
+2. Wait 500ms</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Typing indicator removed</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>ML_122</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Read/Delivery Receipts</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>hideReceipts=false, message sent</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Verify delivery receipt shown on sent message</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Wait for delivery</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Double tick/delivered indicator appears</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>ML_123</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Read/Delivery Receipts</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Message delivered and read</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Verify read receipt shown on sent message</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Recipient reads message</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Blue double tick/read indicator appears</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>ML_124</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Sticky Date Header</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>hideStickyDate=false, scrolling through messages</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Verify sticky date header appears while scrolling</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat with messages across multiple days
+2. Scroll through messages</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Sticky date header shows current date section</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>ML_125</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Date Separator</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>hideDateSeparator=false</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Verify date separators between different day messages</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat with multi-day messages</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Date separator labels shown between day groups</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>ML_126</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Scroll to Bottom</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>User scrolled up in message list</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Verify scroll to bottom button appears</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>1. Scroll up in message list
+2. Check for scroll button</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Scroll to bottom button visible</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>ML_127</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>New Messages Banner</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>User scrolled up, new message arrives</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Verify new messages banner appears</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>1. Scroll up
+2. Receive new message</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>New messages banner shown with count</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>ML_128</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Message Information</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>hideMessageInfoOption=false</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Verify message info option shows delivery/read details</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on sent message
+2. Click message info</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Message info popup shows sent, delivered, read timestamps</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>ML_129</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Go To Message</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>goToMessageId set</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Verify message list scrolls to specific message</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>1. Set goToMessageId prop
+2. Open message list</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>List scrolls to and highlights the target message</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>ML_011</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Verify Message List Display</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, no messages in conversation</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty message list state</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>1. Open a new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>ML_018</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>Verify Reactions</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>Verify reaction fails without network</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to add a reaction.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>Error message should display or reaction should queue for retry.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>ML_030</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Verify Copy Message</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>Verify copy not available for media-only messages</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>1. Long press on an image/video message with no caption.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>'Copy' option should not appear or be disabled for media-only messages.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>ML_034</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Verify Edit Message</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Verify 'Edit' not available for others' messages</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>'Edit' option should NOT appear for messages sent by other users.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>ML_042</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Message</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Verify 'Delete' not available for others' messages</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>ML_043</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Verify delete fails without network</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to delete a message.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display indicating network issue.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>ML_047</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>Verify Notifications</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>User has notifications disabled</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>Verify no notification when disabled</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>1. Disable notifications in settings.
 2. Receive a message.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t>No push notification should appear.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>ML_130</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Message Translation Hidden</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>hideTranslateMessageOption=true</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Verify translate option hidden when disabled</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions menu</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Translate option not visible</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>ML_131</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Flag Message Hidden</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>hideFlagMessageOption=true</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Verify flag option hidden when disabled</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions menu</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Flag message option not visible</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>ML_132</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Message Privately Hidden</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>hideMessagePrivatelyOption=true</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Verify message privately option hidden</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message in group
+2. Check actions</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Message privately option not visible</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>ML_133</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Mark as Unread Hidden</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>showMarkAsUnreadOption=false (default)</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Verify mark as unread not shown by default</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Mark as unread option not visible</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>ML_134</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies Disabled</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>showSmartReplies=false</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Verify smart replies don't appear</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive question message
+2. Wait</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>No smart reply suggestions shown</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>ML_135</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Receipts Hidden</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>hideReceipts=true</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Verify no receipt indicators shown</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Check for ticks</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>No delivery/read indicators visible</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>ML_136</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Sticky Date Hidden</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>hideStickyDate=true</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Verify sticky date header not shown</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>1. Scroll through messages</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>No sticky date header appears</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>ML_137</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Moderation Hidden</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>hideModerationView=true</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Verify moderation status not shown</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>1. Check moderated messages</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>No moderation status indicators visible</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>ML_138</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Flag Remark Hidden</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>hideFlagRemarkField=true</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Verify remark field hidden in flag dialog</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>1. Click flag option
+2. Check dialog</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>No remark text area in flag dialog</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>ML_139</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Translation Failure</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Network disconnected during translation</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Verify error handling for failed translation</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Click translate</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Error message shown, original message intact</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2686,308 +4375,567 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_064</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Message List with Composer</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify sent message from composer appears in message list</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type a message in composer.
 2. Send.
 3. Observe message list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Sent message should immediately appear in message list at the bottom with correct content and timestamp.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_065</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Integration: Message List with Conversation List</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify message list updates reflect in conversation list preview</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Go back to conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Conversation preview should show the latest sent message text and updated timestamp.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ML_066</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Integration: Message List with User Profile</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify tapping user avatar opens user profile</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Tap on a user's avatar in message list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User profile/info panel should open with user details.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ML_067</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Integration: Message List with Real-time Events</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify real-time message delivery from another user</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. User B sends a message to User A.
 2. Observe User A's message list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Message should appear in real-time without manual refresh.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ML_068</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify typing indicator in message list</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. User B starts typing.
 2. Observe User A's chat.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Typing indicator (e.g., 'User B is typing...') should appear and disappear when typing stops.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ML_069</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Integration: Message List with Read Receipts</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify read receipts (double tick/blue tick)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Receiver reads it.
 3. Observe sender's message.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Message should show read receipt indicator (blue double tick or similar).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>ML_070</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify delivered receipt (single/double tick)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Message gets delivered but not read.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Message should show delivered indicator (double grey tick or similar).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ML_140</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Translation + Receipts</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Both features enabled</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify translated message still shows receipts</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Translate a sent message
+2. Check receipts</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Both translation and receipt indicators visible</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ML_141</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies + Send</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies visible</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify smart reply integrates with message sending flow</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Click smart reply
+2. Verify in message list</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Smart reply appears as sent message with receipts</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ML_142</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Forward + Thread</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Threaded message exists</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Verify forwarding a threaded message</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. Open thread
+2. Forward parent message</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Message forwarded with thread context</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ML_143</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Flag + Moderation</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Both enabled</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify flagged message triggers moderation</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. Flag a message
+2. Check moderation status</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Flagged message enters moderation queue</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ML_144</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Mark Unread + Conversation List</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Mark as unread used</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation list updates unread count</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. Mark message as unread
+2. Go to conversation list</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Conversation shows updated unread count</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ML_145</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Forward to Blocked User</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Target user is blocked</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot forward to blocked user</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to forward message
+2. Select blocked user</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Error or blocked user not shown in forward list</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2999,200 +4947,375 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_071</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Message List after actions</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify message list intact after editing a message</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Edit a message.
 2. Observe entire message list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Only edited message should change. All other messages should remain intact with correct order.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_072</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify message list intact after deleting a message</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Delete a message.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Deleted message should be removed/replaced. All other messages unaffected.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ML_073</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify message list after switching between conversations</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation A.
 2. Switch to conversation B.
 3. Switch back to A.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Conversation A should reload with correct messages. No message mixing between conversations.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ML_074</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify message list after app backgrounding and resuming</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Open a chat.
 2. Background the app for 5 minutes.
 3. Resume.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Message list should refresh with any new messages received while backgrounded.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ML_146</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Translation After Edit</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Message edited after translation</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify translation updates after message edit</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Translate message
+2. Sender edits message
+3. Re-translate</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Updated translation shown</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ML_147</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Receipts After Reconnect</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Network reconnected</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify receipts update after reconnection</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message offline
+2. Reconnect</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Receipt status updates correctly</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ML_148</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies After Scroll</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>User scrolled up then back</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify smart replies persist after scrolling</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. See smart replies
+2. Scroll up
+3. Scroll back down</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies still visible</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ML_149</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Flag After Delete</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Message deleted</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot flag deleted message</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Delete message
+2. Try to flag</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Flag option not available for deleted messages</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3204,246 +5327,364 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_075</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Security: Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify messages only visible to conversation participants</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login as User A.
 2. Open a conversation with User B.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_076</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify message content not exposed in URL or logs</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Send messages.
 2. Check browser URL bar and console logs.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ML_078</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify SQL injection prevention in messages</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Message should display as plain text. No database errors or data loss.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ML_079</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify message with malicious URL</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Send a message with a phishing/malicious URL.
+2. Observe link preview.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ML_150</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Flag XSS Prevention</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Malicious script in remark</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify XSS sanitized in flag remark field</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; in remark
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Script tags sanitized, no execution</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ML_151</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Translation Auth</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Valid auth token</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify translation requires authentication</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt translation without login</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Translation fails with auth error</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ML_077</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Security: Message List</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify XSS prevention in message display</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
 2. Observe in receiver's message list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ML_078</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify SQL injection prevention in messages</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Message should display as plain text. No database errors or data loss.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>ML_079</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify message with malicious URL</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message with a phishing/malicious URL.
-2. Observe link preview.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ML_152</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Forward Unauthorized</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>User not in group</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot forward to unauthorized group</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Try forwarding to private group user hasn't joined</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Forward fails with permission error</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3459,330 +5700,533 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_080</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify message list with 10000+ messages in conversation</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Open a conversation with 10000+ messages.
 2. Scroll through.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_081</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify message with only whitespace/spaces</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with only spaces.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Message should either be blocked from sending or display as empty bubble.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ML_082</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify message with mixed RTL and LTR text</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Text should render correctly with proper bidirectional formatting.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ML_083</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify message with 50+ emojis</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with 50+ emojis.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>All emojis should render correctly. No performance issues or layout breaking.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ML_084</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify simultaneous messages from multiple users in group</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Have 10 users send messages simultaneously in a group.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ML_085</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify message with extremely long single word (no spaces)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with a 1000-character word with no spaces.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ML_087</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify message list with corrupted/invalid message data</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Simulate receiving a message with missing or malformed fields.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ML_153</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Translate Long Message</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Message with 10000+ characters</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify translation handles very long messages</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Translate extremely long message</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Translation completes or shows appropriate limit message</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ML_154</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay 0</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=0</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify instant smart replies with 0 delay</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive question
+2. Check immediately</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies appear instantly</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ML_155</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Multiple Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3+ users typing in group</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Verify multiple typing indicators shown</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. Multiple users type simultaneously</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Shows 'X, Y and others are typing'</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>ML_086</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Message List</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify message list when WebSocket disconnects</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Simulate WebSocket disconnection during active chat.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>ML_087</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify message list with corrupted/invalid message data</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Simulate receiving a message with missing or malformed fields.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ML_156</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Forward to Self</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>User tries to forward to themselves</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Verify handling of self-forward</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. Try forwarding message to self</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate handling (allowed or prevented)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ML_157</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Unicode in Flag Remark</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Emoji and special chars in remark</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Verify unicode handling in flag remark</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter emoji/unicode in remark
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Remark saved correctly with unicode</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3798,220 +6242,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_088</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify message with exactly 1 character</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Send a single character 'a'.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should display correctly in a properly sized bubble.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_089</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify message with maximum allowed characters</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Message should send and display correctly. May need 'Read more' expansion.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ML_090</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify message at character limit + 1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ML_091</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify reaction with maximum number of unique reactions</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Add the maximum number of different reaction emojis to a single message.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ML_092</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify message list with exactly 0 messages (new conversation)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Open a brand new conversation with no messages.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Empty state should display. Composer should be ready for first message.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ML_158</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay Min</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=0</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify minimum delay value works</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Set delay to 0
+2. Receive question</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies appear with no delay</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ML_159</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay Default</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=10000</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify default 10s delay works</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Use default delay
+2. Receive question
+3. Wait 10s</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Smart replies appear after 10 seconds</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ML_160</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Quick Options Count 1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify only 1 option shown in quick menu</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=1
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Only 1 action visible, rest in overflow</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ML_161</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Quick Options Count 0</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=0</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Verify 0 quick options hides quick menu</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=0
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>No quick options shown, all in overflow menu</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4027,328 +6645,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ML_093</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Message Types</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify short text message (1-50 chars)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with 25 characters.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should display in a compact bubble.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ML_094</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify medium text message (51-500 chars)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with 250 characters.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Message should display in a medium-sized bubble with proper wrapping.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ML_095</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify long text message (501-5000 chars)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with 2500 characters.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Message should display with 'Read more' or expandable view.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ML_096</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify very long text message (5000+ chars)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Send a message with 10000 characters.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Message should handle gracefully with expansion option. No performance issues.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ML_097</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Media Sizes</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify small image (&lt;100KB)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Send an image under 100KB.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Image should upload quickly and display as thumbnail.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ML_098</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify medium image (100KB-5MB)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Send an image of 2MB.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Image should upload with progress indicator and display correctly.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>ML_099</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify large image (5MB-25MB)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Send an image of 15MB.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Image should upload with progress bar. May take longer. Should complete successfully.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ML_162</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Translation - Text Message</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Text message type</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify translation works for text messages</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Translate a text message</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Text message translated successfully</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ML_163</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Flag - Own Message</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>User's own sent message</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify flagging own message behavior</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to flag own message</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate behavior (allowed or option hidden)</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ML_164</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Receipts - User Chat</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1-on-1 chat</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Verify receipts in direct messages</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message in 1-on-1 chat
+2. Check receipts</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Delivery and read receipts shown</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ML_165</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Receipts - Group Chat</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Group chat</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify receipts in group messages</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. Send message in group
+2. Check receipts</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Delivery receipts shown for group</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ML_100</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify oversized image (&gt;25MB or above limit)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Try to send an image exceeding the file size limit.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Error message should display. File should not upload.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ML_166</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Translation - Media Message</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Image/video message</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Verify translation not available for media</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. Hover on image message
+2. Check for translate</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Translate option not shown for media messages</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,11 +81,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +100,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,3849 +529,4332 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>ML_001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Verify Message List Display</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify message list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Open any conversation.
 2. Observe message list area.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Messages should load and display in chronological order with sender info and timestamps.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ML_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify sender message alignment (right side)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Observe sent messages.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Sender's messages should appear on the right side of the chat.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>ML_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify receiver message alignment (left side)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Observe received messages.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Receiver's messages should appear on the left side of the chat.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ML_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify user name displayed above messages</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Observe messages from different users.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Sender's name should display above their message bubble in group chats.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>ML_005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify user avatar displayed next to messages</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Observe avatars next to messages.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Sender's avatar/profile picture should display next to their messages.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ML_006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify message timestamp display</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Observe timestamps on messages.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Each message should display time in readable format (e.g., '02:35 PM').</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ML_007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify date separator between different days</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Open a conversation with messages spanning multiple days.
 2. Observe date separators.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Date separator (e.g., 'Today', 'Yesterday', 'Feb 15, 2025') should appear between messages of different days.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>ML_008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify scroll to load older messages</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Open a conversation with many messages.
 2. Scroll up to the top.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Older messages should load as user scrolls up. Loading indicator should appear during fetch.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ML_009</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify auto-scroll to latest message on open</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Open a conversation with many messages.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Chat should auto-scroll to the most recent message at the bottom.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ML_010</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify new incoming message auto-scrolls</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Be at the bottom of a conversation.
 2. Receive a new message.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Chat should auto-scroll to show the new incoming message.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ML_013</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Verify Reactions</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify adding a reaction to a message</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on a message.
 2. Select a reaction emoji.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Reaction should appear below the message with count of 1.</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ML_014</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify multiple reactions on a message</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Add different reactions from different users on the same message.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>All unique reactions should display below the message with respective counts.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>ML_015</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify reaction count increments</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Have multiple users react with the same emoji on a message.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Reaction count should increment correctly (e.g., 👍 3).</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>ML_016</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify removing own reaction</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Tap on your own reaction on a message.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Reaction should be removed. Count should decrement or reaction should disappear if count reaches 0.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>ML_017</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Verify reaction details/list</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. Long press or click on a reaction below a message.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>List of users who reacted with that emoji should display.</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>ML_019</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Verify Reply</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify reply option available on message</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on a message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Reply option should be available in the message action menu.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>ML_020</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Verify reply shows original message preview</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>1. Select reply on a message.
 2. Observe composer area.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Original message preview should appear above the input field with close button.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>ML_021</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Verify sending a reply message</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. Select reply on a message.
 2. Type reply text.
 3. Send.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Reply should appear in chat with reference to the original message (quoted).</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>ML_022</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Verify tapping on replied message scrolls to original</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>1. Tap on the quoted/original message in a reply bubble.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Chat should scroll to the original message and highlight it briefly.</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>ML_023</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Verify cancel reply</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. Select reply on a message.
 2. Click close/cancel on the reply preview.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Reply preview should dismiss and composer should return to normal state.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>ML_024</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Verify Reply In Thread</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Verify 'Reply In Thread' option in message menu</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on a message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>'Reply In Thread' option should be available.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>ML_025</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Verify thread panel opens on 'Reply In Thread'</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Reply In Thread' on a message.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Thread panel should open showing the original message and thread replies.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>ML_026</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Verify thread reply count on parent message</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1. Reply in a thread.
 2. Go back to main chat.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Parent message should show thread reply count (e.g., '3 replies').</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>ML_027</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Verify clicking thread count opens thread</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. Click on thread reply count on a parent message.</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Thread panel should open with all thread replies.</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>ML_028</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Verify Copy Message</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Verify 'Copy' option in message menu</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on a text message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>'Copy' option should be available.</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>ML_029</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Verify copying text message</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Copy' on a text message.
 2. Paste in input field.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Message text should be copied to clipboard and paste correctly.</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>ML_031</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Verify Edit Message</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Verify 'Edit' option for own messages</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on own sent text message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>'Edit' option should be available for own messages only.</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>ML_032</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verify editing a message</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Edit' on own message.
 2. Modify text.
 3. Save/Send.</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Message should update with new text and show 'edited' indicator.</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>ML_033</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Verify cancel edit</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Edit' on own message.
 2. Click cancel.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Edit mode should dismiss and original message should remain unchanged.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>ML_035</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Verify Message Info</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verify 'Info' option in message menu</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on own message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>'Info' option should be available.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>ML_036</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Verify message info shows delivery details</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Info' on own message.</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Message info panel should show sent time, delivered time, and read time.</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>ML_037</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Verify message info in group shows read/delivered by</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Info' on own message in a group chat.</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Info should show list of members with delivered and read status for each.</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>ML_038</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Message</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Verify 'Delete' option for own messages</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. Long press or hover on own message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>'Delete' option should be available for own messages.</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>ML_039</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Verify delete confirmation dialog</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Delete' on own message.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>ML_040</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Verify message deleted on confirm</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Message should be removed or replaced with 'This message was deleted' text.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>ML_041</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Verify cancel delete keeps message</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Message should remain unchanged in the chat.</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>ML_044</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Verify Notifications</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>User is logged in and app is in background</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Verify push notification for new message</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. Send a message from another user.
 2. Observe notification on device.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Push notification should appear with sender name and message preview.</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>ML_045</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Verify notification tap opens correct conversation</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>1. Receive a notification.
 2. Tap on it.</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>App should open and navigate to the correct conversation with the new message.</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>ML_046</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open in foreground</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Verify in-app notification for message in different chat</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>1. Be in conversation A.
 2. Receive message in conversation B.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>In-app notification/banner should appear for the new message in conversation B.</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>ML_048</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Verify Calling from Message List</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Verify audio call button in chat header</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Observe chat header.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Audio call icon should be visible in the chat header.</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>ML_049</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Verify video call button in chat header</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Observe chat header.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Video call icon should be visible in the chat header.</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>ML_050</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Verify initiating audio call from chat</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>1. Click audio call icon in chat header.</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Audio call should initiate with the user. Call screen should appear.</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>ML_051</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Verify initiating video call from chat</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>1. Click video call icon in chat header.</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Video call should initiate with the user. Video call screen should appear.</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>ML_052</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Verify group call button in group chat header</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Observe chat header.</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Group call icon should be visible in the group chat header.</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>ML_053</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Verify Group Actions in Message List</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Verify group info accessible from chat header</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Click on group name or info icon in header.</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Group info panel should open showing group details, members, and actions.</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>ML_054</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Verify member join/leave messages in chat</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>1. Have a member join or leave the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>System message should appear (e.g., 'John joined the group', 'Jane left the group').</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>ML_055</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Verify admin action messages in chat</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>1. Admin kicks/bans a member or changes scope.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>System message should appear reflecting the admin action.</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>ML_056</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Verify Message Types Display</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Verify text message display</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>1. Send/receive a text message.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Text message should display in a message bubble with proper formatting.</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>ML_057</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Verify image message display</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>1. Send/receive an image.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Image should display as thumbnail in chat. Tapping should open full-size preview.</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>ML_058</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Verify video message display</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>1. Send/receive a video.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Video thumbnail with play icon should display. Tapping should play the video.</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>ML_059</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Verify audio message display</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1. Send/receive an audio message.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Audio player with play/pause button and duration should display.</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>ML_060</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Verify document/file message display</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. Send/receive a document.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>File icon with file name and size should display. Tapping should download/open.</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>ML_061</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Verify link preview in message</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1. Send a message containing a URL.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Link preview with title, description, and thumbnail should display below the message.</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>ML_062</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Verify sticker message display</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>1. Send/receive a sticker.
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Sticker should display as a larger image without message bubble.</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>ML_063</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Verify emoji-only message display</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>1. Send a message with only emojis (1-3).
 2. Observe in message list.</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Emojis should display in larger size without message bubble background.</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>ML_012</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Verify message list behavior without network</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Open a conversation.</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Cached messages should display or appropriate error message should show.</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>ML_043</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Verify delete fails without network</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to delete a message.</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Error message should display indicating network issue.</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>ML_101</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Message Translation</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>User logged in, translation enabled</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Verify translate message option appears in message actions</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. Open chat
 2. Long press/hover on message
 3. Check for translate option</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>Translate option visible in message actions menu</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>ML_102</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Message Translation</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Message received in foreign language</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Verify message translates to user's language on click</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>1. Receive foreign language message
 2. Click translate option</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Message translated text displayed below original</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>ML_103</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Message Forwarding</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>User logged in with messages</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Verify forward message option in actions menu</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>1. Open chat
 2. Hover on message
 3. Click forward option</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Forward dialog opens with user/group selection</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>ML_104</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Message Forwarding</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Forward dialog open</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Verify message forwards to selected user</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>1. Select target user
 2. Click forward/send</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Message forwarded successfully, confirmation shown</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>ML_105</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Message Sharing</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>User logged in with messages</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Verify share message option in actions menu</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Click share option</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Share dialog/native share sheet opens</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>ML_106</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Flag/Report Message</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>User logged in, flag option enabled</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Verify flag message option appears in actions</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check for flag option</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Flag message option visible in actions menu</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>ML_107</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Flag/Report Message</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Flag dialog open</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Verify user can flag message with remark</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>1. Click flag option
 2. Enter remark
 3. Submit</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Message flagged successfully, confirmation shown</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>ML_108</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Flag/Report Message</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>hideFlagRemarkField=false</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Verify remark text area visible in flag dialog</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1. Click flag option
 2. Check for remark field</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Remark text area is visible and editable</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>ML_109</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Download Media</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Media message received (image/video/file)</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Verify media message can be downloaded</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>1. Click on media message
 2. Click download option</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Media file downloads to device</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>ML_110</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Message Privately</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>User in group chat</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Verify send message privately option in group</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>1. Open group chat
 2. Hover on member's message
 3. Click message privately</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Private chat opens with that user</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>ML_111</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Message Privately</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>User in group chat</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Verify reply message privately option</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Click reply privately</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Private reply sent to user outside group</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>ML_112</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>showMarkAsUnreadOption=true</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Verify mark as unread option appears</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>1. Open chat
 2. Hover on message
 3. Check for mark as unread</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Mark as unread option visible in actions</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>ML_113</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Mark as unread option visible</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>Verify marking message as unread works</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>1. Click mark as unread
 2. Go back to conversation list</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Conversation shows unread indicator from that message</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>ML_114</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Smart Replies</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>showSmartReplies=true, incoming message with question</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Verify smart replies appear for incoming questions</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>1. Receive message containing '?'
 2. Wait for smart replies delay</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Smart reply suggestions appear below message list</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>ML_115</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Smart Replies</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Smart replies visible</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Verify clicking smart reply sends message</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>1. Click on a smart reply suggestion</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Smart reply text sent as message</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>ML_116</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Smart Replies Keywords</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>smartRepliesKeywords=['what','when','how']</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>Verify smart replies trigger only for configured keywords</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>1. Receive message with 'what'
 2. Receive message without keywords</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Smart replies appear only for keyword messages</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>ML_117</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Conversation Starters</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>showConversationStarters=true, new chat with no messages</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Verify conversation starters appear in empty chat</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>1. Open new chat with no history</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Conversation starter suggestions displayed</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>ML_118</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Conversation Starters</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Starters visible</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Verify clicking starter sends message</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>1. Click on a conversation starter</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>Starter text sent as message, chat begins</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>ML_119</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Moderation View</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>hideModerationView=false, moderated message exists</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Verify moderation status shown on messages</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>1. Send message in moderated group
 2. Check message status</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>Moderation status (pending/approved/disapproved) visible</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>ML_120</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Typing Indicators</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Another user typing in chat</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>Verify typing indicator appears</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>1. Other user starts typing
 2. Observe message list footer</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>Typing indicator shown with user name</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>ML_121</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Typing Indicators</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>User stops typing</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Verify typing indicator disappears</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>1. Other user stops typing
 2. Wait 500ms</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Typing indicator removed</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>ML_122</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Read/Delivery Receipts</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>hideReceipts=false, message sent</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Verify delivery receipt shown on sent message</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>1. Send message
 2. Wait for delivery</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>Double tick/delivered indicator appears</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>ML_123</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Read/Delivery Receipts</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Message delivered and read</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Verify read receipt shown on sent message</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>1. Send message
 2. Recipient reads message</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Blue double tick/read indicator appears</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>ML_124</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Sticky Date Header</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>hideStickyDate=false, scrolling through messages</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>Verify sticky date header appears while scrolling</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>1. Open chat with messages across multiple days
 2. Scroll through messages</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>Sticky date header shows current date section</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>ML_125</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>Date Separator</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>hideDateSeparator=false</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>Verify date separators between different day messages</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>1. Open chat with multi-day messages</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>Date separator labels shown between day groups</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>ML_126</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>Scroll to Bottom</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>User scrolled up in message list</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>Verify scroll to bottom button appears</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>1. Scroll up in message list
 2. Check for scroll button</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Scroll to bottom button visible</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>ML_127</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>New Messages Banner</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>User scrolled up, new message arrives</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>Verify new messages banner appears</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr">
         <is>
           <t>1. Scroll up
 2. Receive new message</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>New messages banner shown with count</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="H85" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>ML_128</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Message Information</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>hideMessageInfoOption=false</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>Verify message info option shows delivery/read details</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>1. Hover on sent message
 2. Click message info</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>Message info popup shows sent, delivered, read timestamps</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>ML_129</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Go To Message</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>goToMessageId set</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>Verify message list scrolls to specific message</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
         <is>
           <t>1. Set goToMessageId prop
 2. Open message list</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>List scrolls to and highlights the target message</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="88"/>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ML_167</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Message Search - Open Search View</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Conversation open</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Verify search view opens from header</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Click search icon in message header
+2. Observe side panel</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>CometChatSearchView should open in side panel with search input</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>ML_168</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Message Search - Search Messages</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Verify searching messages in conversation</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>1. Type search query
+2. Observe results</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>CometChatSearch should filter messages by uid/guid with limit 30</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>ML_169</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Message Search - Click Result</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Search results displayed</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Verify clicking search result navigates to message</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>1. Search for a message
+2. Click on a result</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Should navigate to that message in the message list via goToMessageId</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>ML_170</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Message Search - Threaded Result</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Search result is a threaded message</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Verify clicking threaded search result opens thread</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>1. Search for a message that's in a thread
+2. Click result</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Thread should open with the parent message, goToMessageId set to clicked message</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>ML_171</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Message Search - Close Search</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Verify closing search view</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>1. Click close button
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Search view should close, showMessagesSearch set to false</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>ML_172</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Message Search - Keyword Highlighting</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Search result clicked</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Verify search keyword is highlighted in messages</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>1. Search for 'hello'
+2. Click a result
+3. Observe message list</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>The word 'hello' should be highlighted in the message list using TextHighlightFormatter</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>ML_173</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>AI Chat - Detect Agentic User</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>User with role '@agentic' exists</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Verify AI assistant chat renders for agentic users</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>1. Select a user with role '@agentic'
+2. Observe message view</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>CometChatAIAssistantChat should render instead of regular messages view</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>ML_174</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>AI Chat - Back Button on Mobile</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>AI chat open on mobile</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Verify back button in AI chat on mobile</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>1. Open AI chat on mobile view
+2. Observe back button</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Back button should be visible (showBackButton=isMobile)</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>ML_175</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>AI Chat - Back Navigation</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>AI chat open</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Verify back button navigates back</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>1. Click back button in AI chat
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Should clear selected item and return to conversation list</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="n"/>
+      <c r="G97" s="6" t="n"/>
+      <c r="H97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>ML_011</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Verify Message List Display</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>User is logged in, no messages in conversation</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>Verify empty message list state</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>1. Open a new conversation with no messages.</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>ML_018</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Verify Reactions</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>Verify reaction fails without network</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to add a reaction.</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>Error message should display or reaction should queue for retry.</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>ML_030</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Verify Copy Message</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>Verify copy not available for media-only messages</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>1. Long press on an image/video message with no caption.</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>'Copy' option should not appear or be disabled for media-only messages.</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>ML_034</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Verify Edit Message</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>Verify 'Edit' not available for others' messages</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>'Edit' option should NOT appear for messages sent by other users.</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>ML_042</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Message</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>Verify 'Delete' not available for others' messages</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>ML_047</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Verify Notifications</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>User has notifications disabled</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>Verify no notification when disabled</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
         <is>
           <t>1. Disable notifications in settings.
 2. Receive a message.</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>No push notification should appear.</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>ML_130</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>Message Translation Hidden</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>hideTranslateMessageOption=true</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>Verify translate option hidden when disabled</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check actions menu</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>Translate option not visible</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>ML_131</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Flag Message Hidden</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>hideFlagMessageOption=true</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Verify flag option hidden when disabled</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check actions menu</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Flag message option not visible</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>ML_132</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Message Privately Hidden</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>hideMessagePrivatelyOption=true</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Verify message privately option hidden</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message in group
 2. Check actions</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Message privately option not visible</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>ML_133</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Mark as Unread Hidden</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>showMarkAsUnreadOption=false (default)</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Verify mark as unread not shown by default</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check actions</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Mark as unread option not visible</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>ML_134</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Smart Replies Disabled</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>showSmartReplies=false</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Verify smart replies don't appear</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Receive question message
 2. Wait</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>No smart reply suggestions shown</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>ML_135</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Receipts Hidden</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>hideReceipts=true</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Verify no receipt indicators shown</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Send message
 2. Check for ticks</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>No delivery/read indicators visible</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>ML_136</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Sticky Date Hidden</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>hideStickyDate=true</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Verify sticky date header not shown</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Scroll through messages</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>No sticky date header appears</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>ML_137</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Moderation Hidden</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>hideModerationView=true</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Verify moderation status not shown</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Check moderated messages</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>No moderation status indicators visible</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>ML_138</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Flag Remark Hidden</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>hideFlagRemarkField=true</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Verify remark field hidden in flag dialog</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Click flag option
 2. Check dialog</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>No remark text area in flag dialog</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>ML_139</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Translation Failure</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Network disconnected during translation</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Verify error handling for failed translation</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network
 2. Click translate</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Error message shown, original message intact</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ML_176</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Message Search - No Results</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for no search results</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for non-existent text
+2. Observe results</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Empty state or no results message should be displayed</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ML_177</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>AI Chat - Non-Agentic User</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Regular user selected</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Verify regular messages view for non-agentic users</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a regular user (role != '@agentic')
+2. Observe view</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Regular CometChatMessages should render, not AI assistant</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4435,505 +4926,633 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>ML_064</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Integration: Message List with Composer</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify sent message from composer appears in message list</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Type a message in composer.
 2. Send.
 3. Observe message list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Sent message should immediately appear in message list at the bottom with correct content and timestamp.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ML_065</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Integration: Message List with Conversation List</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify message list updates reflect in conversation list preview</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Go back to conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Conversation preview should show the latest sent message text and updated timestamp.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>ML_066</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Integration: Message List with User Profile</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify tapping user avatar opens user profile</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Tap on a user's avatar in message list.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>User profile/info panel should open with user details.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ML_067</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Integration: Message List with Real-time Events</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify real-time message delivery from another user</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. User B sends a message to User A.
 2. Observe User A's message list.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Message should appear in real-time without manual refresh.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>ML_068</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify typing indicator in message list</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. User B starts typing.
 2. Observe User A's chat.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Typing indicator (e.g., 'User B is typing...') should appear and disappear when typing stops.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ML_069</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Integration: Message List with Read Receipts</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify read receipts (double tick/blue tick)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Receiver reads it.
 3. Observe sender's message.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Message should show read receipt indicator (blue double tick or similar).</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ML_070</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify delivered receipt (single/double tick)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Message gets delivered but not read.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Message should show delivered indicator (double grey tick or similar).</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>ML_140</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Translation + Receipts</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Both features enabled</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify translated message still shows receipts</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Translate a sent message
 2. Check receipts</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Both translation and receipt indicators visible</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ML_141</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Smart Replies + Send</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Smart replies visible</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify smart reply integrates with message sending flow</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Click smart reply
 2. Verify in message list</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Smart reply appears as sent message with receipts</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ML_142</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Forward + Thread</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Threaded message exists</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify forwarding a threaded message</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Open thread
 2. Forward parent message</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Message forwarded with thread context</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ML_143</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Flag + Moderation</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Both enabled</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify flagged message triggers moderation</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Flag a message
 2. Check moderation status</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Flagged message enters moderation queue</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ML_144</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Mark Unread + Conversation List</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Mark as unread used</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify conversation list updates unread count</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Mark message as unread
 2. Go to conversation list</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Conversation shows updated unread count</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ML_178</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Message Search - User Filter</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Search view open in user chat</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify search filters by user UID</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open search in user conversation
+2. Search for text</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>CometChatSearch should receive uid prop for filtering</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ML_179</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Message Search - Group Filter</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Search view open in group chat</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Verify search filters by group GUID</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1. Open search in group conversation
+2. Search for text</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>CometChatSearch should receive guid prop for filtering</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ML_180</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>AI Chat - User Prop Passing</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Agentic user selected</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify user prop passed to AI component</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Select agentic user
+2. Inspect component props</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>CometChatAIAssistantChat should receive user prop correctly</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ML_145</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Forward to Blocked User</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Target user is blocked</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify cannot forward to blocked user</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Try to forward message
 2. Select blocked user</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Error or blocked user not shown in forward list</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4948,1297 +5567,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ML_071</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Regression: Message List after actions</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list intact after editing a message</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Edit a message.
-2. Observe entire message list.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Only edited message should change. All other messages should remain intact with correct order.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ML_072</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list intact after deleting a message</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Delete a message.
-2. Observe message list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Deleted message should be removed/replaced. All other messages unaffected.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>ML_073</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list after switching between conversations</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Open conversation A.
-2. Switch to conversation B.
-3. Switch back to A.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Conversation A should reload with correct messages. No message mixing between conversations.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ML_074</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list after app backgrounding and resuming</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Open a chat.
-2. Background the app for 5 minutes.
-3. Resume.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Message list should refresh with any new messages received while backgrounded.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ML_146</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Translation After Edit</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Message edited after translation</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify translation updates after message edit</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Translate message
-2. Sender edits message
-3. Re-translate</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Updated translation shown</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ML_147</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Receipts After Reconnect</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Network reconnected</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify receipts update after reconnection</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Send message offline
-2. Reconnect</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Receipt status updates correctly</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ML_148</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Smart Replies After Scroll</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>User scrolled up then back</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify smart replies persist after scrolling</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. See smart replies
-2. Scroll up
-3. Scroll back down</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Smart replies still visible</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ML_149</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Flag After Delete</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Message deleted</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Verify cannot flag deleted message</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. Delete message
-2. Try to flag</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Flag option not available for deleted messages</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C00000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ML_075</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Security: Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify messages only visible to conversation participants</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Login as User A.
-2. Open a conversation with User B.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ML_076</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify message content not exposed in URL or logs</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Send messages.
-2. Check browser URL bar and console logs.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>ML_078</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify SQL injection prevention in messages</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Message should display as plain text. No database errors or data loss.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ML_079</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with malicious URL</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message with a phishing/malicious URL.
-2. Observe link preview.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ML_150</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Flag XSS Prevention</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Malicious script in remark</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify XSS sanitized in flag remark field</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; in remark
-2. Submit</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Script tags sanitized, no execution</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ML_151</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Translation Auth</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Valid auth token</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify translation requires authentication</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Attempt translation without login</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Translation fails with auth error</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ML_077</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Security: Message List</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify XSS prevention in message display</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
-2. Observe in receiver's message list.</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ML_152</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Forward Unauthorized</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>User not in group</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Verify cannot forward to unauthorized group</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. Try forwarding to private group user hasn't joined</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Forward fails with permission error</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ML_080</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list with 10000+ messages in conversation</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Open a conversation with 10000+ messages.
-2. Scroll through.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ML_081</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with only whitespace/spaces</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message with only spaces.
-2. Observe message list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Message should either be blocked from sending or display as empty bubble.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>ML_082</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with mixed RTL and LTR text</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Text should render correctly with proper bidirectional formatting.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ML_083</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with 50+ emojis</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message with 50+ emojis.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>All emojis should render correctly. No performance issues or layout breaking.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ML_084</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify simultaneous messages from multiple users in group</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Have 10 users send messages simultaneously in a group.</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ML_085</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with extremely long single word (no spaces)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message with a 1000-character word with no spaces.</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ML_087</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list with corrupted/invalid message data</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Simulate receiving a message with missing or malformed fields.</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ML_153</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Translate Long Message</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Message with 10000+ characters</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify translation handles very long messages</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Translate extremely long message</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Translation completes or shows appropriate limit message</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ML_154</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Smart Replies Delay 0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>smartRepliesDelayDuration=0</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Verify instant smart replies with 0 delay</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. Receive question
-2. Check immediately</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Smart replies appear instantly</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ML_155</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Multiple Typing Indicators</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>3+ users typing in group</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Verify multiple typing indicators shown</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. Multiple users type simultaneously</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Shows 'X, Y and others are typing'</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ML_086</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: Message List</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list when WebSocket disconnects</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. Simulate WebSocket disconnection during active chat.</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ML_156</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Forward to Self</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>User tries to forward to themselves</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Verify handling of self-forward</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. Try forwarding message to self</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Appropriate handling (allowed or prevented)</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>ML_157</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Unicode in Flag Remark</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Emoji and special chars in remark</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Verify unicode handling in flag remark</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. Enter emoji/unicode in remark
-2. Submit</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Remark saved correctly with unicode</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6298,354 +5626,350 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ML_088</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ML_071</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Boundary: Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Regression: Message List after actions</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with exactly 1 character</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a single character 'a'.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Message should display correctly in a properly sized bubble.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list intact after editing a message</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Edit a message.
+2. Observe entire message list.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Only edited message should change. All other messages should remain intact with correct order.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ML_089</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify message with maximum allowed characters</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Message should send and display correctly. May need 'Read more' expansion.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ML_072</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list intact after deleting a message</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete a message.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Deleted message should be removed/replaced. All other messages unaffected.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>ML_090</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify message at character limit + 1</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ML_073</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list after switching between conversations</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Open conversation A.
+2. Switch to conversation B.
+3. Switch back to A.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Conversation A should reload with correct messages. No message mixing between conversations.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ML_091</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify reaction with maximum number of unique reactions</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Add the maximum number of different reaction emojis to a single message.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ML_074</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list after app backgrounding and resuming</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a chat.
+2. Background the app for 5 minutes.
+3. Resume.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Message list should refresh with any new messages received while backgrounded.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ML_092</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify message list with exactly 0 messages (new conversation)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Open a brand new conversation with no messages.</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Empty state should display. Composer should be ready for first message.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML_146</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Translation After Edit</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Message edited after translation</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify translation updates after message edit</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Translate message
+2. Sender edits message
+3. Re-translate</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Updated translation shown</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ML_158</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ML_147</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Smart Replies Delay Min</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>smartRepliesDelayDuration=0</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify minimum delay value works</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Set delay to 0
-2. Receive question</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Smart replies appear with no delay</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Receipts After Reconnect</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Network reconnected</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify receipts update after reconnection</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Send message offline
+2. Reconnect</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Receipt status updates correctly</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ML_148</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Smart Replies After Scroll</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>User scrolled up then back</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify smart replies persist after scrolling</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. See smart replies
+2. Scroll up
+3. Scroll back down</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Smart replies still visible</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ML_159</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Smart Replies Delay Default</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>smartRepliesDelayDuration=10000</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify default 10s delay works</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Use default delay
-2. Receive question
-3. Wait 10s</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Smart replies appear after 10 seconds</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ML_149</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Flag After Delete</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Message deleted</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify cannot flag deleted message</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete message
+2. Try to flag</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Flag option not available for deleted messages</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ML_160</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Quick Options Count 1</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>quickOptionsCount=1</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify only 1 option shown in quick menu</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Set quickOptionsCount=1
-2. Hover on message</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Only 1 action visible, rest in overflow</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ML_161</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Quick Options Count 0</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>quickOptionsCount=0</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Verify 0 quick options hides quick menu</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. Set quickOptionsCount=0
-2. Hover on message</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>No quick options shown, all in overflow menu</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0000B0F0"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6701,478 +6025,1901 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ML_075</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Security: Message List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify messages only visible to conversation participants</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Login as User A.
+2. Open a conversation with User B.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ML_076</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify message content not exposed in URL or logs</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Send messages.
+2. Check browser URL bar and console logs.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ML_078</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify SQL injection prevention in messages</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Message should display as plain text. No database errors or data loss.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ML_079</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with malicious URL</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with a phishing/malicious URL.
+2. Observe link preview.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML_150</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Flag XSS Prevention</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Malicious script in remark</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify XSS sanitized in flag remark field</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; in remark
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Script tags sanitized, no execution</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ML_151</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Translation Auth</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Valid auth token</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify translation requires authentication</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Attempt translation without login</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Translation fails with auth error</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ML_077</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Security: Message List</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in message display</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
+2. Observe in receiver's message list.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ML_152</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Forward Unauthorized</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>User not in group</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify cannot forward to unauthorized group</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Try forwarding to private group user hasn't joined</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Forward fails with permission error</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ML_080</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list with 10000+ messages in conversation</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a conversation with 10000+ messages.
+2. Scroll through.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ML_081</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with only whitespace/spaces</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with only spaces.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Message should either be blocked from sending or display as empty bubble.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ML_082</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with mixed RTL and LTR text</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Text should render correctly with proper bidirectional formatting.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ML_083</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with 50+ emojis</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with 50+ emojis.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>All emojis should render correctly. No performance issues or layout breaking.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML_084</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify simultaneous messages from multiple users in group</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Have 10 users send messages simultaneously in a group.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ML_085</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with extremely long single word (no spaces)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with a 1000-character word with no spaces.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ML_087</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list with corrupted/invalid message data</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Simulate receiving a message with missing or malformed fields.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ML_153</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Translate Long Message</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Message with 10000+ characters</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify translation handles very long messages</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Translate extremely long message</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Translation completes or shows appropriate limit message</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ML_154</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay 0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=0</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify instant smart replies with 0 delay</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Receive question
+2. Check immediately</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Smart replies appear instantly</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ML_155</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Multiple Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>3+ users typing in group</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Verify multiple typing indicators shown</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. Multiple users type simultaneously</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Shows 'X, Y and others are typing'</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ML_181</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Message Search - Mobile Close Behavior</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Search open on mobile</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify search closes properly on mobile</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open search on mobile view
+2. Click a result</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Search should close, navigate to message in main list</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ML_086</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list when WebSocket disconnects</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>1. Simulate WebSocket disconnection during active chat.</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ML_156</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Forward to Self</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>User tries to forward to themselves</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Verify handling of self-forward</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1. Try forwarding message to self</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Appropriate handling (allowed or prevented)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ML_157</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Unicode in Flag Remark</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Emoji and special chars in remark</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify unicode handling in flag remark</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter emoji/unicode in remark
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Remark saved correctly with unicode</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ML_088</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Boundary: Message List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a single character 'a'.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Message should display correctly in a properly sized bubble.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ML_089</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with maximum allowed characters</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Message should send and display correctly. May need 'Read more' expansion.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ML_090</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify message at character limit + 1</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ML_091</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify reaction with maximum number of unique reactions</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Add the maximum number of different reaction emojis to a single message.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML_092</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list with exactly 0 messages (new conversation)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a brand new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Empty state should display. Composer should be ready for first message.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ML_158</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay Min</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=0</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify minimum delay value works</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Set delay to 0
+2. Receive question</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Smart replies appear with no delay</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ML_159</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay Default</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=10000</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify default 10s delay works</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Use default delay
+2. Receive question
+3. Wait 10s</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Smart replies appear after 10 seconds</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ML_160</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Quick Options Count 1</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=1</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify only 1 option shown in quick menu</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=1
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Only 1 action visible, rest in overflow</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ML_161</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Quick Options Count 0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Verify 0 quick options hides quick menu</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=0
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>No quick options shown, all in overflow menu</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>ML_093</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Message Types</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify short text message (1-50 chars)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Send a message with 25 characters.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Message should display in a compact bubble.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ML_094</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify medium text message (51-500 chars)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Send a message with 250 characters.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Message should display in a medium-sized bubble with proper wrapping.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>ML_095</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify long text message (501-5000 chars)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Send a message with 2500 characters.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Message should display with 'Read more' or expandable view.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ML_096</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify very long text message (5000+ chars)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Send a message with 10000 characters.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Message should handle gracefully with expansion option. No performance issues.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>ML_097</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Media Sizes</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify small image (&lt;100KB)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Send an image under 100KB.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Image should upload quickly and display as thumbnail.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ML_098</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify medium image (100KB-5MB)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Send an image of 2MB.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Image should upload with progress indicator and display correctly.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ML_099</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify large image (5MB-25MB)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Send an image of 15MB.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Image should upload with progress bar. May take longer. Should complete successfully.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>ML_162</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Translation - Text Message</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Text message type</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify translation works for text messages</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Translate a text message</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Text message translated successfully</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ML_163</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Flag - Own Message</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>User's own sent message</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify flagging own message behavior</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Try to flag own message</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Appropriate behavior (allowed or option hidden)</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ML_164</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Receipts - User Chat</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>1-on-1 chat</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify receipts in direct messages</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Send message in 1-on-1 chat
 2. Check receipts</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Delivery and read receipts shown</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ML_165</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Receipts - Group Chat</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Group chat</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify receipts in group messages</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Send message in group
 2. Check receipts</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Delivery receipts shown for group</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>ML_100</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify oversized image (&gt;25MB or above limit)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Try to send an image exceeding the file size limit.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Error message should display. File should not upload.</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>ML_166</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Translation - Media Message</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Image/video message</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify translation not available for media</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Hover on image message
 2. Check for translate</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Translate option not shown for media messages</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +107,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4079,782 +4082,1614 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="n"/>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="6" t="n"/>
-      <c r="H97" s="6" t="n"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>ML_182</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Option Visibility</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Message list open, received message visible</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Verify 'Mark as Unread' option appears on received messages</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a conversation
+2. Right-click/long-press on a received message
+3. Observe context menu options</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Mark as Unread option should be visible in the message actions menu</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>ML_011</t>
+          <t>ML_183</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Verify Message List Display</t>
+          <t>Mark Unread - Execute on Message</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>User is logged in, no messages in conversation</t>
+          <t>Received message visible in chat</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Verify empty message list state</t>
+          <t>Verify marking a specific message as unread</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>1. Open a new conversation with no messages.</t>
+          <t>1. Right-click/long-press a received message
+2. Select 'Mark as Unread'
+3. Observe changes</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+          <t>Message should be marked as unread, conversation shows unread indicator/badge</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
+          <t>ML_184</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Unread Badge on Conversation</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Message marked as unread</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Verify unread count badge appears on conversation list</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Navigate to conversation list
+3. Observe the conversation entry</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Conversation should show unread count badge (e.g., '1' or the actual unread count)</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>ML_185</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - New Messages Divider</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Message marked as unread in chat</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Verify 'New Messages' divider appears at the marked position</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Re-open the conversation
+3. Observe message list</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>A 'New Messages' divider line should appear above the marked message, separating read from unread</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>ML_186</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Scroll Position on Reopen</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Message marked as unread, startFromUnreadMessages enabled</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation opens at the unread position</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Navigate away from conversation
+3. Re-open the same conversation</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Message list should scroll to the last read message position, showing unread messages above the divider</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>ML_187</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Unread Count Display</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Multiple messages after marked position</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Verify correct unread count is shown</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread where 5 messages follow it
+2. Check conversation list badge</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Badge should show the correct unread count (e.g., '5')</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>ML_188</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Clear on Scroll to Bottom</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Unread messages present, banner visible</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Verify unread state clears when user scrolls to bottom</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>1. Open conversation with unread messages
+2. Scroll to the very bottom of the message list</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Unread count should reset to 0, banner disappears, messages marked as read</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>ML_189</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Visual Indicator in List</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Message marked as unread</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Verify visual indicator (bold text/dot/badge) on conversation in list</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Go to conversation list
+3. Observe the conversation item</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Conversation should have a visual unread indicator (bold title, unread count badge, or dot)</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ML_190</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - New Messages Banner</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Unread messages exist, user not at bottom</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Verify new messages banner/count appears in message list</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Open conversation
+3. Observe banner area</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>A banner showing the unread count (e.g., '3 new messages') should appear, allowing quick scroll to bottom</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ML_191</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - 1:1 User Chat</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>1:1 conversation with received messages</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread works in one-on-one chats</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a 1:1 user conversation
+2. Mark a received message as unread
+3. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Unread badge should appear on the 1:1 conversation</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ML_192</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Group Chat</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Group conversation with received messages</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread works in group chats</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a group conversation
+2. Mark a received message as unread
+3. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Unread badge should appear on the group conversation</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ML_193</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - As Reminder to Reply</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Received message requiring follow-up</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread serves as a reply reminder</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>1. Read a message that needs a response later
+2. Mark it as unread
+3. Navigate away
+4. Return to conversation list</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Conversation should remain visually prominent with unread indicator until user reads/responds</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ML_194</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Auto-Clear on Read</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Message previously marked as unread</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread state clears when user reads the messages</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Open the conversation
+3. Scroll through all unread messages to bottom</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Unread indicator should clear, conversation marked as read again</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ML_195</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Count Cap at 999+</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Conversation with 1000+ unread messages</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread count displays as 999+ for large counts</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. Have a conversation with very high unread count
+2. Observe the unread badge</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Badge should display '999+' instead of the exact number when count &gt;= 999</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ML_011</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message List Display</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no messages in conversation</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty message list state</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
           <t>ML_018</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Verify Reactions</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Verify reaction fails without network</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to add a reaction.</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Error message should display or reaction should queue for retry.</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>ML_030</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Verify Copy Message</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Verify copy not available for media-only messages</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Long press on an image/video message with no caption.</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>'Copy' option should not appear or be disabled for media-only messages.</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>ML_034</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Verify Edit Message</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Verify 'Edit' not available for others' messages</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>'Edit' option should NOT appear for messages sent by other users.</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>ML_042</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Message</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Verify 'Delete' not available for others' messages</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Long press on another user's message.
 2. Observe message menu.</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>ML_047</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Verify Notifications</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>User has notifications disabled</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Verify no notification when disabled</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Disable notifications in settings.
 2. Receive a message.</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>No push notification should appear.</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>ML_130</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Message Translation Hidden</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>hideTranslateMessageOption=true</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Verify translate option hidden when disabled</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check actions menu</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>Translate option not visible</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>ML_131</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Flag Message Hidden</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>hideFlagMessageOption=true</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Verify flag option hidden when disabled</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check actions menu</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Flag message option not visible</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>ML_132</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Message Privately Hidden</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>hideMessagePrivatelyOption=true</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Verify message privately option hidden</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message in group
 2. Check actions</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>Message privately option not visible</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>ML_133</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Mark as Unread Hidden</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>showMarkAsUnreadOption=false (default)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Verify mark as unread not shown by default</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Hover on message
 2. Check actions</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>Mark as unread option not visible</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>ML_134</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Smart Replies Disabled</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>showSmartReplies=false</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Verify smart replies don't appear</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Receive question message
 2. Wait</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>No smart reply suggestions shown</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>ML_135</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Receipts Hidden</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>hideReceipts=true</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Verify no receipt indicators shown</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Send message
 2. Check for ticks</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>No delivery/read indicators visible</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>ML_136</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Sticky Date Hidden</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>hideStickyDate=true</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Verify sticky date header not shown</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Scroll through messages</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>No sticky date header appears</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>ML_137</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>Moderation Hidden</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>hideModerationView=true</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Verify moderation status not shown</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Check moderated messages</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>No moderation status indicators visible</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>ML_138</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Flag Remark Hidden</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>hideFlagRemarkField=true</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Verify remark field hidden in flag dialog</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Click flag option
 2. Check dialog</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>No remark text area in flag dialog</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>ML_139</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>Translation Failure</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Network disconnected during translation</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Verify error handling for failed translation</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network
 2. Click translate</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>Error message shown, original message intact</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>ML_176</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Message Search - No Results</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Search view open</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Verify empty state for no search results</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Search for non-existent text
 2. Observe results</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>Empty state or no results message should be displayed</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>ML_177</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>AI Chat - Non-Agentic User</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Regular user selected</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Verify regular messages view for non-agentic users</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Select a regular user (role != '@agentic')
 2. Observe view</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>Regular CometChatMessages should render, not AI assistant</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>ML_196</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Not Available on Own Messages</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Message list with sent messages</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Mark as Unread' option is NOT shown on own sent messages</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>1. Right-click/long-press on a message you sent
+2. Observe context menu</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Mark as Unread option should NOT appear for messages sent by the logged-in user</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ML_197</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Hidden When Disabled</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>showMarkAsUnreadOption set to false</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Verify option is hidden when feature is disabled</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>1. Configure MessageList with showMarkAsUnreadOption=false
+2. Right-click a received message
+3. Observe menu</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Mark as Unread option should not appear in the context menu</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>ML_198</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Duplicate Mark Prevention</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Same message already marked as unread</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking the same message twice is prevented</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a received message as unread
+2. Immediately try to mark the same message as unread again</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Second attempt should be silently ignored (no duplicate API call)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>ML_199</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Does Not Undo Read Receipts</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Message already read with read receipts on</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking as unread does NOT remove read receipts for the sender</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>1. Read a message (blue ticks/read receipt sent)
+2. Mark it as unread
+3. Check sender's view</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Sender should still see read receipts (blue ticks). Mark as unread is a local/personal reminder only</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>ML_200</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Not on Action Messages</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Group action message visible (e.g., 'User joined')</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread not available on system/action messages</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>1. Find a system action message in group chat
+2. Try to right-click/long-press
+3. Observe options</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Mark as Unread should not be available on system/action messages</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4870,7 +5705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5515,46 +6350,349 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ML_201</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - SDK API Call</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Received message in conversation</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify CometChat.markMessageAsUnread() SDK call is made</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Monitor SDK API calls</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>CometChat.markMessageAsUnread(message) should be called with the correct message object</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>ML_202</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Conversation List Update Event</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Message marked as unread</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify ccUpdateConversation event fires to update conversation list</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Monitor CometChatConversationEvents</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>ccUpdateConversation event should fire with updated conversation object containing new unread count</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ML_203</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Last Read Message ID Update</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Message marked as unread</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify lastReadMessageId is updated from returned conversation</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark message as unread
+2. Check lastReadMessageId state</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>lastReadMessageId should be updated from conversation.getLastReadMessageId()</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ML_204</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Unread Count From Conversation</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Message marked as unread</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread count is fetched from conversation object</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark message as unread
+2. Check unreadMessagesCount</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Unread count should be set from conversation.getUnreadMessageCount()</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ML_205</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Start From Unread Integration</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>startFromUnreadMessages=true, message marked unread</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list starts from unread position on reopen</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Close conversation
+3. Reopen it</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Message list should fetch conversation, get lastReadMessageId, and scroll to that position</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ML_206</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Cross-Device Sync</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>User logged in on multiple devices</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread state syncs across devices via server</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread on Device A
+2. Open the same conversation on Device B</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Unread state should be reflected on Device B (server-side unread count updated)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>ML_145</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Forward to Blocked User</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Target user is blocked</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verify cannot forward to blocked user</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Try to forward message
 2. Select blocked user</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Error or blocked user not shown in forward list</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ML_207</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - API Failure Handling</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Network error during mark as unread</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Verify error handling when SDK call fails</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Try to mark a message as unread
+3. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Error should be caught by errorHandler, app should not crash, user should see graceful failure</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5570,7 +6708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5895,67 +7033,190 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ML_208</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - New Messages After Marking</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Message marked as unread, new messages arrive</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread count updates when new messages arrive after marking</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread (count shows 3)
+2. Receive 2 new messages while away
+3. Check count</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Unread count should increase to include both marked-unread and newly received messages</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>ML_209</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Send Message Clears Unread</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Messages marked as unread in conversation</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify sending a message clears unread state</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark messages as unread
+2. Open conversation
+3. Send a new message</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Sending a message should mark conversation as read, clearing unread count</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ML_210</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - After Unblock User</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User was blocked then unblocked</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread works after unblocking a user</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Block a user
+2. Unblock the user
+3. Receive messages
+4. Mark a message as unread</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mark as unread should work normally after unblock</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>ML_149</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Flag After Delete</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Message deleted</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify cannot flag deleted message</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Delete message
 2. Try to flag</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Flag option not available for deleted messages</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5966,988 +7227,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>ML_075</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Security: Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Verify messages only visible to conversation participants</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>1. Login as User A.
-2. Open a conversation with User B.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ML_076</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Verify message content not exposed in URL or logs</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1. Send messages.
-2. Check browser URL bar and console logs.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ML_078</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Verify SQL injection prevention in messages</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Message should display as plain text. No database errors or data loss.</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ML_079</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Verify message with malicious URL</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message with a phishing/malicious URL.
-2. Observe link preview.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ML_150</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Flag XSS Prevention</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Malicious script in remark</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Verify XSS sanitized in flag remark field</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; in remark
-2. Submit</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Script tags sanitized, no execution</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ML_151</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Translation Auth</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Valid auth token</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Verify translation requires authentication</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1. Attempt translation without login</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Translation fails with auth error</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>ML_077</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Security: Message List</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Verify XSS prevention in message display</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
-2. Observe in receiver's message list.</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ML_152</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Forward Unauthorized</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>User not in group</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Verify cannot forward to unauthorized group</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>1. Try forwarding to private group user hasn't joined</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Forward fails with permission error</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>ML_080</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Edge Case: Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Verify message list with 10000+ messages in conversation</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a conversation with 10000+ messages.
-2. Scroll through.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ML_081</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Verify message with only whitespace/spaces</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message with only spaces.
-2. Observe message list.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Message should either be blocked from sending or display as empty bubble.</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ML_082</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Verify message with mixed RTL and LTR text</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Text should render correctly with proper bidirectional formatting.</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ML_083</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Verify message with 50+ emojis</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message with 50+ emojis.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>All emojis should render correctly. No performance issues or layout breaking.</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ML_084</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Verify simultaneous messages from multiple users in group</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1. Have 10 users send messages simultaneously in a group.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ML_085</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Verify message with extremely long single word (no spaces)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1. Send a message with a 1000-character word with no spaces.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ML_087</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Verify message list with corrupted/invalid message data</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>1. Simulate receiving a message with missing or malformed fields.</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>ML_153</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Translate Long Message</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Message with 10000+ characters</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Verify translation handles very long messages</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. Translate extremely long message</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Translation completes or shows appropriate limit message</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ML_154</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Smart Replies Delay 0</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>smartRepliesDelayDuration=0</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Verify instant smart replies with 0 delay</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>1. Receive question
-2. Check immediately</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Smart replies appear instantly</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>ML_155</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Multiple Typing Indicators</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>3+ users typing in group</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Verify multiple typing indicators shown</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1. Multiple users type simultaneously</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Shows 'X, Y and others are typing'</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>ML_181</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Message Search - Mobile Close Behavior</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Search open on mobile</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify search closes properly on mobile</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Open search on mobile view
-2. Click a result</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Search should close, navigate to message in main list</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ML_086</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Edge Case: Message List</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Verify message list when WebSocket disconnects</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>1. Simulate WebSocket disconnection during active chat.</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>ML_156</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Forward to Self</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>User tries to forward to themselves</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Verify handling of self-forward</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>1. Try forwarding message to self</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Appropriate handling (allowed or prevented)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>ML_157</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Unicode in Flag Remark</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Emoji and special chars in remark</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify unicode handling in flag remark</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter emoji/unicode in remark
-2. Submit</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Remark saved correctly with unicode</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7009,7 +7288,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ML_088</t>
+          <t>ML_075</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -7019,39 +7298,40 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Boundary: Message List</t>
+          <t>Security: Message List</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Verify message with exactly 1 character</t>
+          <t>Verify messages only visible to conversation participants</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1. Send a single character 'a'.</t>
+          <t>1. Login as User A.
+2. Open a conversation with User B.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Message should display correctly in a properly sized bubble.</t>
+          <t>Only messages between A and B should display. No messages from other conversations should leak.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ML_089</t>
+          <t>ML_076</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -7059,29 +7339,30 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Verify message with maximum allowed characters</t>
+          <t>Verify message content not exposed in URL or logs</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
+          <t>1. Send messages.
+2. Check browser URL bar and console logs.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Message should send and display correctly. May need 'Read more' expansion.</t>
+          <t>Message content should not appear in URLs, query parameters, or client-side logs.</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ML_090</t>
+          <t>ML_078</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -7089,29 +7370,29 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Verify message at character limit + 1</t>
+          <t>Verify SQL injection prevention in messages</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
+          <t>1. Send a message containing SQL injection payload (e.g., "'; DROP TABLE messages;--").</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
+          <t>Message should display as plain text. No database errors or data loss.</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ML_091</t>
+          <t>ML_079</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -7119,59 +7400,73 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Verify reaction with maximum number of unique reactions</t>
+          <t>Verify message with malicious URL</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1. Add the maximum number of different reaction emojis to a single message.</t>
+          <t>1. Send a message with a phishing/malicious URL.
+2. Observe link preview.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
+          <t>Link should be clickable but app should warn about external links or have URL validation.</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Medium / High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ML_092</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+          <t>ML_150</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Flag XSS Prevention</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Malicious script in remark</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Verify message list with exactly 0 messages (new conversation)</t>
+          <t>Verify XSS sanitized in flag remark field</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1. Open a brand new conversation with no messages.</t>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; in remark
+2. Submit</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Empty state should display. Composer should be ready for first message.</t>
+          <t>Script tags sanitized, no execution</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ML_158</t>
+          <t>ML_151</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -7181,199 +7476,225 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Smart Replies Delay Min</t>
+          <t>Translation Auth</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>smartRepliesDelayDuration=0</t>
+          <t>Valid auth token</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Verify minimum delay value works</t>
+          <t>Verify translation requires authentication</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1. Set delay to 0
-2. Receive question</t>
+          <t>1. Attempt translation without login</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Smart replies appear with no delay</t>
+          <t>Translation fails with auth error</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ML_159</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Smart Replies Delay Default</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>smartRepliesDelayDuration=10000</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Verify default 10s delay works</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>1. Use default delay
-2. Receive question
-3. Wait 10s</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Smart replies appear after 10 seconds</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ML_160</t>
+          <t>ML_077</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Quick Options Count 1</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>quickOptionsCount=1</t>
-        </is>
-      </c>
+          <t>Security: Message List</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Verify only 1 option shown in quick menu</t>
+          <t>Verify XSS prevention in message display</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1. Set quickOptionsCount=1
-2. Hover on message</t>
+          <t>1. Send a message containing '&lt;script&gt;alert(1)&lt;/script&gt;'.
+2. Observe in receiver's message list.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Only 1 action visible, rest in overflow</t>
+          <t>Script should NOT execute. HTML should be escaped/sanitized and displayed as plain text.</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ML_152</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Forward Unauthorized</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>User not in group</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify cannot forward to unauthorized group</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Try forwarding to private group user hasn't joined</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Forward fails with permission error</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>ML_161</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ML_211</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Quick Options Count 0</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>quickOptionsCount=0</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Verify 0 quick options hides quick menu</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1. Set quickOptionsCount=0
-2. Hover on message</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>No quick options shown, all in overflow menu</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - No Impact on Other Users</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Message marked as unread</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking as unread has no security impact on other users</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Check if any data is sent to the message sender</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No notification or status change should be sent to the sender. This is a local/personal action only</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ML_212</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Requires Authentication</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User not logged in</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread requires valid authentication</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Attempt to call markMessageAsUnread without valid auth
+2. Observe response</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SDK should reject the call with authentication error</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0000B0F0"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7431,7 +7752,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ML_093</t>
+          <t>ML_080</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -7441,7 +7762,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Equivalence Partitioning: Message Types</t>
+          <t>Edge Case: Message List</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -7451,17 +7772,18 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Verify short text message (1-50 chars)</t>
+          <t>Verify message list with 10000+ messages in conversation</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1. Send a message with 25 characters.</t>
+          <t>1. Open a conversation with 10000+ messages.
+2. Scroll through.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Message should display in a compact bubble.</t>
+          <t>Messages should load via pagination. No memory leak, crash, or extreme slowness.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -7473,7 +7795,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ML_094</t>
+          <t>ML_081</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -7481,29 +7803,30 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Verify medium text message (51-500 chars)</t>
+          <t>Verify message with only whitespace/spaces</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1. Send a message with 250 characters.</t>
+          <t>1. Send a message with only spaces.
+2. Observe message list.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Message should display in a medium-sized bubble with proper wrapping.</t>
+          <t>Message should either be blocked from sending or display as empty bubble.</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ML_095</t>
+          <t>ML_082</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -7511,29 +7834,29 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Verify long text message (501-5000 chars)</t>
+          <t>Verify message with mixed RTL and LTR text</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1. Send a message with 2500 characters.</t>
+          <t>1. Send a message mixing Arabic/Hebrew with English text.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Message should display with 'Read more' or expandable view.</t>
+          <t>Text should render correctly with proper bidirectional formatting.</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ML_096</t>
+          <t>ML_083</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -7541,51 +7864,47 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Verify very long text message (5000+ chars)</t>
+          <t>Verify message with 50+ emojis</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1. Send a message with 10000 characters.</t>
+          <t>1. Send a message with 50+ emojis.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Message should handle gracefully with expansion option. No performance issues.</t>
+          <t>All emojis should render correctly. No performance issues or layout breaking.</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ML_097</t>
+          <t>ML_084</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning: Media Sizes</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Verify small image (&lt;100KB)</t>
+          <t>Verify simultaneous messages from multiple users in group</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1. Send an image under 100KB.</t>
+          <t>1. Have 10 users send messages simultaneously in a group.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Image should upload quickly and display as thumbnail.</t>
+          <t>All messages should appear in correct chronological order. No duplicates or missing messages.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -7597,7 +7916,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ML_098</t>
+          <t>ML_085</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -7605,29 +7924,29 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Verify medium image (100KB-5MB)</t>
+          <t>Verify message with extremely long single word (no spaces)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1. Send an image of 2MB.</t>
+          <t>1. Send a message with a 1000-character word with no spaces.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Image should upload with progress indicator and display correctly.</t>
+          <t>Message bubble should handle word-break/overflow. No horizontal scrolling or layout break.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ML_099</t>
+          <t>ML_087</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
@@ -7635,17 +7954,17 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Verify large image (5MB-25MB)</t>
+          <t>Verify message list with corrupted/invalid message data</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1. Send an image of 15MB.</t>
+          <t>1. Simulate receiving a message with missing or malformed fields.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Image should upload with progress bar. May take longer. Should complete successfully.</t>
+          <t>App should handle gracefully — skip or show placeholder. No crash.</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -7657,7 +7976,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ML_162</t>
+          <t>ML_153</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -7667,39 +7986,39 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Translation - Text Message</t>
+          <t>Translate Long Message</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Text message type</t>
+          <t>Message with 10000+ characters</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Verify translation works for text messages</t>
+          <t>Verify translation handles very long messages</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1. Translate a text message</t>
+          <t>1. Translate extremely long message</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Text message translated successfully</t>
+          <t>Translation completes or shows appropriate limit message</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ML_163</t>
+          <t>ML_154</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -7709,27 +8028,28 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Flag - Own Message</t>
+          <t>Smart Replies Delay 0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>User's own sent message</t>
+          <t>smartRepliesDelayDuration=0</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Verify flagging own message behavior</t>
+          <t>Verify instant smart replies with 0 delay</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1. Try to flag own message</t>
+          <t>1. Receive question
+2. Check immediately</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Appropriate behavior (allowed or option hidden)</t>
+          <t>Smart replies appear instantly</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -7741,6 +8061,1471 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>ML_155</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Multiple Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>3+ users typing in group</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Verify multiple typing indicators shown</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. Multiple users type simultaneously</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Shows 'X, Y and others are typing'</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ML_181</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Message Search - Mobile Close Behavior</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Search open on mobile</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify search closes properly on mobile</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open search on mobile view
+2. Click a result</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Search should close, navigate to message in main list</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ML_213</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Oldest Message in Chat</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Long conversation history</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Verify marking the very first/oldest message as unread</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>1. Scroll to the oldest message in conversation
+2. Mark it as unread
+3. Check unread count</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>All messages in the conversation should be counted as unread</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ML_214</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Last Message in Chat</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Conversation with messages</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Verify marking the most recent message as unread</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark the last/newest received message as unread
+2. Check unread count</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Unread count should show 1, divider should appear before the last message</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ML_215</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Rapid Mark and Open</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Conversation with messages</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Verify rapid mark-unread then immediately open conversation</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread
+2. Immediately open the same conversation
+3. Scroll to bottom</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Unread state should be set then cleared properly without race conditions</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ML_216</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - During Active Conversation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Active conversation with incoming messages</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking as unread while new messages are arriving</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Be in an active conversation
+2. Mark an older message as unread while new messages arrive</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mark as unread should work correctly, unread count should include both marked and new messages</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ML_217</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Multiple Conversations</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Multiple conversations available</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking messages as unread in multiple conversations</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread in Conversation A
+2. Mark a message as unread in Conversation B
+3. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Both conversations should show unread badges independently</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ML_218</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Single Message Conversation</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Conversation with exactly 1 received message</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking unread in a conversation with only one message</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation with single received message
+2. Mark it as unread</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Unread count should show 1, conversation should show unread indicator</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ML_086</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify message list when WebSocket disconnects</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate WebSocket disconnection during active chat.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ML_156</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Forward to Self</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>User tries to forward to themselves</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Verify handling of self-forward</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Try forwarding message to self</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate handling (allowed or prevented)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ML_157</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Unicode in Flag Remark</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Emoji and special chars in remark</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verify unicode handling in flag remark</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter emoji/unicode in remark
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Remark saved correctly with unicode</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ML_219</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Offline State</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Device is offline</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Verify behavior when marking as unread while offline</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Go offline
+2. Try to mark a message as unread
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Should fail gracefully with error handling, no crash</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ML_088</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Boundary: Message List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a single character 'a'.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Message should display correctly in a properly sized bubble.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ML_089</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify message with maximum allowed characters</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message at the maximum character limit (e.g., 65535 chars).</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Message should send and display correctly. May need 'Read more' expansion.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ML_090</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify message at character limit + 1</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to send a message exceeding the maximum character limit by 1.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Message should be blocked or truncated. Appropriate error/warning should display.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ML_091</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify reaction with maximum number of unique reactions</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Add the maximum number of different reaction emojis to a single message.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>All reactions should display. UI should handle overflow (e.g., '+5 more').</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML_092</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify message list with exactly 0 messages (new conversation)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a brand new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Empty state should display. Composer should be ready for first message.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ML_158</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay Min</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=0</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify minimum delay value works</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Set delay to 0
+2. Receive question</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Smart replies appear with no delay</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ML_159</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Smart Replies Delay Default</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>smartRepliesDelayDuration=10000</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify default 10s delay works</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Use default delay
+2. Receive question
+3. Wait 10s</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Smart replies appear after 10 seconds</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ML_160</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Quick Options Count 1</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=1</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify only 1 option shown in quick menu</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=1
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Only 1 action visible, rest in overflow</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ML_220</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Exactly 999 Unread Count</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Conversation with exactly 999 unread messages</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify display at 999 boundary</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Have exactly 999 unread messages
+2. Observe badge</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Badge should show '999' (not '999+')</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ML_221</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - 1000 Unread Count</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Conversation with 1000 unread messages</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Verify display at 1000 boundary</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. Have 1000 unread messages
+2. Observe badge</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Badge should show '999+' (cap triggered)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ML_222</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Minimum Unread Count (1)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Single message marked as unread</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify minimum unread count display</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark exactly 1 message as unread
+2. Observe badge</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Badge should show '1'</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ML_223</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Zero After Clear</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Previously unread, now scrolled to bottom</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify count goes to exactly 0 after clearing</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Have unread messages
+2. Scroll to bottom to clear
+3. Check count</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Unread count should be exactly 0, no badge shown</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ML_161</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Quick Options Count 0</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify 0 quick options hides quick menu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=0
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No quick options shown, all in overflow menu</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ML_093</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Message Types</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify short text message (1-50 chars)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with 25 characters.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Message should display in a compact bubble.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ML_094</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify medium text message (51-500 chars)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with 250 characters.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Message should display in a medium-sized bubble with proper wrapping.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ML_095</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify long text message (501-5000 chars)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with 2500 characters.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Message should display with 'Read more' or expandable view.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ML_096</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify very long text message (5000+ chars)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a message with 10000 characters.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Message should handle gracefully with expansion option. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML_097</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Media Sizes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify small image (&lt;100KB)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Send an image under 100KB.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Image should upload quickly and display as thumbnail.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ML_098</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify medium image (100KB-5MB)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Send an image of 2MB.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Image should upload with progress indicator and display correctly.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ML_099</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify large image (5MB-25MB)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Send an image of 15MB.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Image should upload with progress bar. May take longer. Should complete successfully.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ML_162</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Translation - Text Message</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Text message type</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify translation works for text messages</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Translate a text message</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Text message translated successfully</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ML_163</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Flag - Own Message</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>User's own sent message</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify flagging own message behavior</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to flag own message</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Appropriate behavior (allowed or option hidden)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>ML_164</t>
         </is>
       </c>
@@ -7825,101 +9610,306 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ML_224</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Text Message</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Received text message</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread on text message type</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Right-click a received text message
+2. Select Mark as Unread</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Should work correctly for text messages</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ML_100</t>
+          <t>ML_225</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Media Message</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Received media message (image/video/file)</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Verify oversized image (&gt;25MB or above limit)</t>
+          <t>Verify mark as unread on media message type</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1. Try to send an image exceeding the file size limit.</t>
+          <t>1. Right-click a received media message
+2. Select Mark as Unread</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Error message should display. File should not upload.</t>
+          <t>Should work correctly for media messages</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>ML_226</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Mark Unread - Custom Message</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Received custom message type</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Verify mark as unread on custom message type</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1. Right-click a received custom message
+2. Select Mark as Unread</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Should work correctly for custom message types</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ML_227</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Middle of Conversation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Long conversation, message in the middle</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking a message in the middle of conversation</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Scroll to middle of conversation
+2. Mark a received message as unread</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>All messages after the marked one should count as unread</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ML_100</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify oversized image (&gt;25MB or above limit)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to send an image exceeding the file size limit.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display. File should not upload.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>ML_166</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Translation - Media Message</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Image/video message</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verify translation not available for media</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Hover on image message
 2. Check for translate</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Translate option not shown for media messages</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ML_228</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mark Unread - Own Sent Message</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Own sent message in conversation</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify mark as unread unavailable on own messages</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Right-click own sent message
+2. Check for Mark as Unread option</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Option should NOT be present for sent messages</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -79,7 +79,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -94,6 +94,34 @@
       <bottom style="thin"/>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -496,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4112,528 +4140,1308 @@
       <c r="H97" s="10" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="n"/>
-      <c r="C98" s="12" t="n"/>
-      <c r="D98" s="12" t="n"/>
-      <c r="E98" s="12" t="n"/>
-      <c r="F98" s="12" t="n"/>
-      <c r="G98" s="12" t="n"/>
-      <c r="H98" s="12" t="n"/>
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>ML_011</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Verify Message List Display</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in, no messages in conversation</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Verify empty message list state</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>1. Open a new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
+          <t>ML_018</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Verify Reactions</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Verify reaction fails without network</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to add a reaction.</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>Error message should display or reaction should queue for retry.</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>ML_030</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Verify Copy Message</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Verify copy not available for media-only messages</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>1. Long press on an image/video message with no caption.</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>ML_034</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Verify Edit Message</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Edit' not available for others' messages</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>'Edit' option should NOT appear for messages sent by other users.</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>ML_042</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Verify Delete Message</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Delete' not available for others' messages</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>ML_047</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Verify Notifications</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>User has notifications disabled</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Verify no notification when disabled</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>1. Disable notifications in settings.
+2. Receive a message.</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>No push notification should appear.</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>ML_130</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Message Translation Hidden</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>hideTranslateMessageOption=true</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Verify translate option hidden when disabled</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions menu</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Translate option not visible</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>ML_131</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Flag Message Hidden</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>hideFlagMessageOption=true</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Verify flag option hidden when disabled</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions menu</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Flag message option not visible</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>ML_132</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Message Privately Hidden</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>hideMessagePrivatelyOption=true</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Verify message privately option hidden</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message in group
+2. Check actions</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>Message privately option not visible</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>ML_133</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Mark as Unread Hidden</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>showMarkAsUnreadOption=false (default)</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Verify mark as unread not shown by default</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>Mark as unread option not visible</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>ML_134</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Smart Replies Disabled</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>showSmartReplies=false</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Verify smart replies don't appear</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>1. Receive question message
+2. Wait</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>No smart reply suggestions shown</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>ML_135</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Receipts Hidden</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>hideReceipts=true</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Verify no receipt indicators shown</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Check for ticks</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>No delivery/read indicators visible</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>ML_136</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Sticky Date Hidden</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>hideStickyDate=true</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Verify sticky date header not shown</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>1. Scroll through messages</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>No sticky date header appears</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>ML_137</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Moderation Hidden</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>hideModerationView=true</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Verify moderation status not shown</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>1. Check moderated messages</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>No moderation status indicators visible</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>ML_138</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Flag Remark Hidden</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>hideFlagRemarkField=true</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Verify remark field hidden in flag dialog</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>1. Click flag option
+2. Check dialog</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>No remark text area in flag dialog</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>ML_139</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Translation Failure</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Network disconnected during translation</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>Verify error handling for failed translation</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Click translate</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>Error message shown, original message intact</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>ML_176</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - No Results</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>Verify empty state for no search results</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>1. Search for non-existent text
+2. Observe results</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>Empty state or no results message should be displayed</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>ML_177</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>AI Chat - Non-Agentic User</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Regular user selected</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Verify regular messages view for non-agentic users</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>1. Select a regular user (role != '@agentic')
+2. Observe view</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>Regular CometChatMessages should render, not AI assistant</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n"/>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="10" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
+      <c r="H116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>Mark as Unread</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n"/>
+      <c r="C117" s="12" t="n"/>
+      <c r="D117" s="12" t="n"/>
+      <c r="E117" s="12" t="n"/>
+      <c r="F117" s="12" t="n"/>
+      <c r="G117" s="12" t="n"/>
+      <c r="H117" s="12" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
           <t>ML_182</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Option Visibility</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
         <is>
           <t>Message list open, received message visible</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E118" s="9" t="inlineStr">
         <is>
           <t>Verify 'Mark as Unread' option appears on received messages</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F118" s="9" t="inlineStr">
         <is>
           <t>1. Open a conversation
 2. Right-click/long-press on a received message
 3. Observe context menu options</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
+      <c r="G118" s="9" t="inlineStr">
         <is>
           <t>Mark as Unread option should be visible in the message actions menu</t>
         </is>
       </c>
-      <c r="H99" s="9" t="inlineStr">
+      <c r="H118" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>ML_183</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Execute on Message</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>Received message visible in chat</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="E119" s="9" t="inlineStr">
         <is>
           <t>Verify marking a specific message as unread</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr">
         <is>
           <t>1. Right-click/long-press a received message
 2. Select 'Mark as Unread'
 3. Observe changes</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>Message should be marked as unread, conversation shows unread indicator/badge</t>
         </is>
       </c>
-      <c r="H100" s="9" t="inlineStr">
+      <c r="H119" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>ML_184</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Unread Badge on Conversation</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread</t>
         </is>
       </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="E120" s="9" t="inlineStr">
         <is>
           <t>Verify unread count badge appears on conversation list</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Navigate to conversation list
 3. Observe the conversation entry</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="G120" s="9" t="inlineStr">
         <is>
           <t>Conversation should show unread count badge (e.g., '1' or the actual unread count)</t>
         </is>
       </c>
-      <c r="H101" s="9" t="inlineStr">
+      <c r="H120" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>ML_185</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - New Messages Divider</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D121" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread in chat</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E121" s="9" t="inlineStr">
         <is>
           <t>Verify 'New Messages' divider appears at the marked position</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Re-open the conversation
 3. Observe message list</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>A 'New Messages' divider line should appear above the marked message, separating read from unread</t>
         </is>
       </c>
-      <c r="H102" s="9" t="inlineStr">
+      <c r="H121" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>ML_186</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Scroll Position on Reopen</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread, startFromUnreadMessages enabled</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="E122" s="9" t="inlineStr">
         <is>
           <t>Verify conversation opens at the unread position</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F122" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Navigate away from conversation
 3. Re-open the same conversation</t>
         </is>
       </c>
-      <c r="G103" s="9" t="inlineStr">
+      <c r="G122" s="9" t="inlineStr">
         <is>
           <t>Message list should scroll to the last read message position, showing unread messages above the divider</t>
         </is>
       </c>
-      <c r="H103" s="9" t="inlineStr">
+      <c r="H122" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>ML_187</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Unread Count Display</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>Multiple messages after marked position</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr">
         <is>
           <t>Verify correct unread count is shown</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread where 5 messages follow it
 2. Check conversation list badge</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr">
+      <c r="G123" s="9" t="inlineStr">
         <is>
           <t>Badge should show the correct unread count (e.g., '5')</t>
         </is>
       </c>
-      <c r="H104" s="9" t="inlineStr">
+      <c r="H123" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>ML_188</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Clear on Scroll to Bottom</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>Unread messages present, banner visible</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="E124" s="9" t="inlineStr">
         <is>
           <t>Verify unread state clears when user scrolls to bottom</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F124" s="9" t="inlineStr">
         <is>
           <t>1. Open conversation with unread messages
 2. Scroll to the very bottom of the message list</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G124" s="9" t="inlineStr">
         <is>
           <t>Unread count should reset to 0, banner disappears, messages marked as read</t>
         </is>
       </c>
-      <c r="H105" s="9" t="inlineStr">
+      <c r="H124" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>ML_189</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Visual Indicator in List</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>Verify visual indicator (bold text/dot/badge) on conversation in list</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Go to conversation list
 3. Observe the conversation item</t>
         </is>
       </c>
-      <c r="G106" s="9" t="inlineStr">
+      <c r="G125" s="9" t="inlineStr">
         <is>
           <t>Conversation should have a visual unread indicator (bold title, unread count badge, or dot)</t>
         </is>
       </c>
-      <c r="H106" s="9" t="inlineStr">
+      <c r="H125" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>ML_190</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - New Messages Banner</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>Unread messages exist, user not at bottom</t>
         </is>
       </c>
-      <c r="E107" s="9" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>Verify new messages banner/count appears in message list</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F126" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Open conversation
 3. Observe banner area</t>
         </is>
       </c>
-      <c r="G107" s="9" t="inlineStr">
+      <c r="G126" s="9" t="inlineStr">
         <is>
           <t>A banner showing the unread count (e.g., '3 new messages') should appear, allowing quick scroll to bottom</t>
         </is>
       </c>
-      <c r="H107" s="9" t="inlineStr">
+      <c r="H126" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>ML_191</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - 1:1 User Chat</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>1:1 conversation with received messages</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread works in one-on-one chats</t>
         </is>
       </c>
-      <c r="F108" s="9" t="inlineStr">
+      <c r="F127" s="9" t="inlineStr">
         <is>
           <t>1. Open a 1:1 user conversation
 2. Mark a received message as unread
 3. Check conversation list</t>
         </is>
       </c>
-      <c r="G108" s="9" t="inlineStr">
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>Unread badge should appear on the 1:1 conversation</t>
         </is>
       </c>
-      <c r="H108" s="9" t="inlineStr">
+      <c r="H127" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>ML_192</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Group Chat</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>Group conversation with received messages</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread works in group chats</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F128" s="9" t="inlineStr">
         <is>
           <t>1. Open a group conversation
 2. Mark a received message as unread
 3. Check conversation list</t>
         </is>
       </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="G128" s="9" t="inlineStr">
         <is>
           <t>Unread badge should appear on the group conversation</t>
         </is>
       </c>
-      <c r="H109" s="9" t="inlineStr">
+      <c r="H128" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>ML_193</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - As Reminder to Reply</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>Received message requiring follow-up</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread serves as a reply reminder</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
         <is>
           <t>1. Read a message that needs a response later
 2. Mark it as unread
@@ -4641,881 +5449,101 @@
 4. Return to conversation list</t>
         </is>
       </c>
-      <c r="G110" s="9" t="inlineStr">
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>Conversation should remain visually prominent with unread indicator until user reads/responds</t>
         </is>
       </c>
-      <c r="H110" s="9" t="inlineStr">
+      <c r="H129" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>ML_194</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Auto-Clear on Read</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>Message previously marked as unread</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>Verify unread state clears when user reads the messages</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F130" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Open the conversation
 3. Scroll through all unread messages to bottom</t>
         </is>
       </c>
-      <c r="G111" s="9" t="inlineStr">
+      <c r="G130" s="9" t="inlineStr">
         <is>
           <t>Unread indicator should clear, conversation marked as read again</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr">
+      <c r="H130" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>ML_195</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Count Cap at 999+</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>Conversation with 1000+ unread messages</t>
         </is>
       </c>
-      <c r="E112" s="9" t="inlineStr">
+      <c r="E131" s="9" t="inlineStr">
         <is>
           <t>Verify unread count displays as 999+ for large counts</t>
         </is>
       </c>
-      <c r="F112" s="9" t="inlineStr">
+      <c r="F131" s="9" t="inlineStr">
         <is>
           <t>1. Have a conversation with very high unread count
 2. Observe the unread badge</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
+      <c r="G131" s="9" t="inlineStr">
         <is>
           <t>Badge should display '999+' instead of the exact number when count &gt;= 999</t>
         </is>
       </c>
-      <c r="H112" s="9" t="inlineStr">
+      <c r="H131" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="n"/>
-      <c r="B113" s="10" t="n"/>
-      <c r="C113" s="10" t="n"/>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>ML_011</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>Verify Message List Display</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in, no messages in conversation</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>Verify empty message list state</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>1. Open a new conversation with no messages.</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>ML_018</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>Verify Reactions</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>Verify reaction fails without network</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to add a reaction.</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>Error message should display or reaction should queue for retry.</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>ML_030</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>Verify Copy Message</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>Verify copy not available for media-only messages</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>1. Long press on an image/video message with no caption.</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
-        </is>
-      </c>
-      <c r="H116" s="9" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>ML_034</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>Verify Edit Message</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>Verify 'Edit' not available for others' messages</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
-        <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>'Edit' option should NOT appear for messages sent by other users.</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>ML_042</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>Verify Delete Message</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>Verify 'Delete' not available for others' messages</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>ML_047</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>Verify Notifications</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>User has notifications disabled</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>Verify no notification when disabled</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
-        <is>
-          <t>1. Disable notifications in settings.
-2. Receive a message.</t>
-        </is>
-      </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>No push notification should appear.</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>ML_130</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>Message Translation Hidden</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>hideTranslateMessageOption=true</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>Verify translate option hidden when disabled</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message
-2. Check actions menu</t>
-        </is>
-      </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>Translate option not visible</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>ML_131</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>Flag Message Hidden</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>hideFlagMessageOption=true</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>Verify flag option hidden when disabled</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message
-2. Check actions menu</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>Flag message option not visible</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>ML_132</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>Message Privately Hidden</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>hideMessagePrivatelyOption=true</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>Verify message privately option hidden</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message in group
-2. Check actions</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>Message privately option not visible</t>
-        </is>
-      </c>
-      <c r="H122" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>ML_133</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>Mark as Unread Hidden</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>showMarkAsUnreadOption=false (default)</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>Verify mark as unread not shown by default</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message
-2. Check actions</t>
-        </is>
-      </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>Mark as unread option not visible</t>
-        </is>
-      </c>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>ML_134</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>Smart Replies Disabled</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>showSmartReplies=false</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>Verify smart replies don't appear</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>1. Receive question message
-2. Wait</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>No smart reply suggestions shown</t>
-        </is>
-      </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>ML_135</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>Receipts Hidden</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>hideReceipts=true</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>Verify no receipt indicators shown</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>1. Send message
-2. Check for ticks</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>No delivery/read indicators visible</t>
-        </is>
-      </c>
-      <c r="H125" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>ML_136</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>Sticky Date Hidden</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>hideStickyDate=true</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>Verify sticky date header not shown</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>1. Scroll through messages</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>No sticky date header appears</t>
-        </is>
-      </c>
-      <c r="H126" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>ML_137</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>Moderation Hidden</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>hideModerationView=true</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>Verify moderation status not shown</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="inlineStr">
-        <is>
-          <t>1. Check moderated messages</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>No moderation status indicators visible</t>
-        </is>
-      </c>
-      <c r="H127" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>ML_138</t>
-        </is>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>Flag Remark Hidden</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>hideFlagRemarkField=true</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>Verify remark field hidden in flag dialog</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>1. Click flag option
-2. Check dialog</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>No remark text area in flag dialog</t>
-        </is>
-      </c>
-      <c r="H128" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>ML_139</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>Translation Failure</t>
-        </is>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>Network disconnected during translation</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="inlineStr">
-        <is>
-          <t>Verify error handling for failed translation</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr">
-        <is>
-          <t>1. Disconnect network
-2. Click translate</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>Error message shown, original message intact</t>
-        </is>
-      </c>
-      <c r="H129" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t>ML_176</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - No Results</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
-        <is>
-          <t>Search view open</t>
-        </is>
-      </c>
-      <c r="E130" s="9" t="inlineStr">
-        <is>
-          <t>Verify empty state for no search results</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>1. Search for non-existent text
-2. Observe results</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>Empty state or no results message should be displayed</t>
-        </is>
-      </c>
-      <c r="H130" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="9" t="inlineStr">
-        <is>
-          <t>ML_177</t>
-        </is>
-      </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>AI Chat - Non-Agentic User</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>Regular user selected</t>
-        </is>
-      </c>
-      <c r="E131" s="9" t="inlineStr">
-        <is>
-          <t>Verify regular messages view for non-agentic users</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>1. Select a regular user (role != '@agentic')
-2. Observe view</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>Regular CometChatMessages should render, not AI assistant</t>
-        </is>
-      </c>
-      <c r="H131" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
         </is>
       </c>
     </row>
@@ -5530,23 +5558,52 @@
       <c r="H132" s="10" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="n"/>
-      <c r="C133" s="12" t="n"/>
-      <c r="D133" s="12" t="n"/>
-      <c r="E133" s="12" t="n"/>
-      <c r="F133" s="12" t="n"/>
-      <c r="G133" s="12" t="n"/>
-      <c r="H133" s="12" t="n"/>
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>ML_196</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Mark Unread - Not Available on Own Messages</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>Message list with sent messages</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Mark as Unread' option is NOT shown on own sent messages</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>1. Right-click/long-press on a message you sent
+2. Observe context menu</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>Mark as Unread option should NOT appear for messages sent by the logged-in user</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>ML_196</t>
+          <t>ML_197</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -5556,72 +5613,72 @@
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Mark Unread - Not Available on Own Messages</t>
+          <t>Mark Unread - Hidden When Disabled</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Message list with sent messages</t>
+          <t>showMarkAsUnreadOption set to false</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>Verify 'Mark as Unread' option is NOT shown on own sent messages</t>
+          <t>Verify option is hidden when feature is disabled</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr">
-        <is>
-          <t>1. Right-click/long-press on a message you sent
-2. Observe context menu</t>
-        </is>
-      </c>
-      <c r="G134" s="9" t="inlineStr">
-        <is>
-          <t>Mark as Unread option should NOT appear for messages sent by the logged-in user</t>
-        </is>
-      </c>
-      <c r="H134" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>ML_197</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>Mark Unread - Hidden When Disabled</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>showMarkAsUnreadOption set to false</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>Verify option is hidden when feature is disabled</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>1. Configure MessageList with showMarkAsUnreadOption=false
 2. Right-click a received message
 3. Observe menu</t>
         </is>
       </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>Mark as Unread option should not appear in the context menu</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>ML_198</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Mark Unread - Duplicate Mark Prevention</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>Same message already marked as unread</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>Verify marking the same message twice is prevented</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>1. Mark a received message as unread
+2. Immediately try to mark the same message as unread again</t>
+        </is>
+      </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Mark as Unread option should not appear in the context menu</t>
+          <t>Second attempt should be silently ignored (no duplicate API call)</t>
         </is>
       </c>
       <c r="H135" s="9" t="inlineStr">
@@ -5633,7 +5690,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>ML_198</t>
+          <t>ML_199</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -5643,128 +5700,134 @@
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Mark Unread - Duplicate Mark Prevention</t>
+          <t>Mark Unread - Does Not Undo Read Receipts</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Same message already marked as unread</t>
+          <t>Message already read with read receipts on</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Verify marking the same message twice is prevented</t>
+          <t>Verify marking as unread does NOT remove read receipts for the sender</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>1. Mark a received message as unread
-2. Immediately try to mark the same message as unread again</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr">
-        <is>
-          <t>Second attempt should be silently ignored (no duplicate API call)</t>
-        </is>
-      </c>
-      <c r="H136" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>ML_199</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>Mark Unread - Does Not Undo Read Receipts</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>Message already read with read receipts on</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>Verify marking as unread does NOT remove read receipts for the sender</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
         <is>
           <t>1. Read a message (blue ticks/read receipt sent)
 2. Mark it as unread
 3. Check sender's view</t>
         </is>
       </c>
-      <c r="G137" s="9" t="inlineStr">
+      <c r="G136" s="9" t="inlineStr">
         <is>
           <t>Sender should still see read receipts (blue ticks). Mark as unread is a local/personal reminder only</t>
         </is>
       </c>
-      <c r="H137" s="9" t="inlineStr">
+      <c r="H136" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="9" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>ML_200</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B137" s="9" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C137" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Not on Action Messages</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>Group action message visible (e.g., 'User joined')</t>
         </is>
       </c>
-      <c r="E138" s="9" t="inlineStr">
+      <c r="E137" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread not available on system/action messages</t>
         </is>
       </c>
-      <c r="F138" s="9" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr">
         <is>
           <t>1. Find a system action message in group chat
 2. Try to right-click/long-press
 3. Observe options</t>
         </is>
       </c>
-      <c r="G138" s="9" t="inlineStr">
+      <c r="G137" s="9" t="inlineStr">
         <is>
           <t>Mark as Unread should not be available on system/action messages</t>
         </is>
       </c>
-      <c r="H138" s="9" t="inlineStr">
+      <c r="H137" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="10" t="n"/>
+      <c r="B138" s="10" t="n"/>
+      <c r="C138" s="10" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="10" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="n"/>
+      <c r="B139" s="10" t="n"/>
+      <c r="C139" s="10" t="n"/>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="10" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="n"/>
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="10" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="n"/>
+      <c r="B141" s="10" t="n"/>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="10" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="n"/>
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="10" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A133:H133"/>
-    <mergeCell ref="A98:H98"/>
+  <mergeCells count="1">
+    <mergeCell ref="A117:H117"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5777,7 +5840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6390,371 +6453,371 @@
       <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>ML_145</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Forward to Blocked User</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Target user is blocked</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Verify cannot forward to blocked user</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>1. Try to forward message
+2. Select blocked user</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Error or blocked user not shown in forward list</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>ML_144</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Mark Unread + Conversation List</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Mark as unread used</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Verify conversation list updates unread count</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>1. Mark message as unread
 2. Go to conversation list</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Conversation shows updated unread count</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ML_201</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - SDK API Call</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Received message in conversation</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Verify CometChat.markMessageAsUnread() SDK call is made</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Monitor SDK API calls</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>CometChat.markMessageAsUnread(message) should be called with the correct message object</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>ML_202</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Conversation List Update Event</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Verify ccUpdateConversation event fires to update conversation list</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Monitor CometChatConversationEvents</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>ccUpdateConversation event should fire with updated conversation object containing new unread count</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>ML_203</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Last Read Message ID Update</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Verify lastReadMessageId is updated from returned conversation</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>1. Mark message as unread
 2. Check lastReadMessageId state</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>lastReadMessageId should be updated from conversation.getLastReadMessageId()</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>ML_204</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Unread Count From Conversation</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Verify unread count is fetched from conversation object</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>1. Mark message as unread
 2. Check unreadMessagesCount</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Unread count should be set from conversation.getUnreadMessageCount()</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ML_205</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Start From Unread Integration</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>startFromUnreadMessages=true, message marked unread</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Verify message list starts from unread position on reopen</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Close conversation
 3. Reopen it</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Message list should fetch conversation, get lastReadMessageId, and scroll to that position</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>ML_206</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Cross-Device Sync</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>User logged in on multiple devices</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Verify unread state syncs across devices via server</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread on Device A
 2. Open the same conversation on Device B</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Unread state should be reflected on Device B (server-side unread count updated)</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>ML_145</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Forward to Blocked User</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Target user is blocked</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Verify cannot forward to blocked user</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>1. Try to forward message
-2. Select blocked user</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Error or blocked user not shown in forward list</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -6769,67 +6832,102 @@
       <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>ML_207</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - API Failure Handling</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Network error during mark as unread</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Verify error handling when SDK call fails</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>1. Disconnect network
 2. Try to mark a message as unread
 3. Observe behavior</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>Error should be caught by errorHandler, app should not crash, user should see graceful failure</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A17:H17"/>
+  <mergeCells count="1">
+    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6842,7 +6940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7177,134 +7275,187 @@
       <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ML_149</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Flag After Delete</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Message deleted</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Verify cannot flag deleted message</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>1. Delete message
+2. Try to flag</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Flag option not available for deleted messages</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>ML_208</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - New Messages After Marking</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread, new messages arrive</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Verify unread count updates when new messages arrive after marking</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread (count shows 3)
 2. Receive 2 new messages while away
 3. Check count</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Unread count should increase to include both marked-unread and newly received messages</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>ML_209</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Send Message Clears Unread</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Messages marked as unread in conversation</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Verify sending a message clears unread state</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>1. Mark messages as unread
 2. Open conversation
 3. Send a new message</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Sending a message should mark conversation as read, clearing unread count</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>ML_210</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - After Unblock User</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>User was blocked then unblocked</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread works after unblocking a user</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>1. Block a user
 2. Unblock the user
@@ -7312,62 +7463,9 @@
 4. Mark a message as unread</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Mark as unread should work normally after unblock</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>ML_149</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Flag After Delete</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Message deleted</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Verify cannot flag deleted message</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>1. Delete message
-2. Try to flag</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Flag option not available for deleted messages</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -7396,9 +7494,49 @@
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7411,7 +7549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7906,6 +8044,46 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
       <c r="H16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7922,7 +8100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8382,405 +8560,405 @@
       <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>ML_086</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Edge Case: Message List</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Verify message list when WebSocket disconnects</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>1. Simulate WebSocket disconnection during active chat.</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
+          <t>ML_156</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Forward to Self</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>User tries to forward to themselves</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Verify handling of self-forward</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>1. Try forwarding message to self</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Appropriate handling (allowed or prevented)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>ML_157</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Unicode in Flag Remark</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Emoji and special chars in remark</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Verify unicode handling in flag remark</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>1. Enter emoji/unicode in remark
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Remark saved correctly with unicode</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Mark as Unread</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
           <t>ML_213</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Oldest Message in Chat</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Long conversation history</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Verify marking the very first/oldest message as unread</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>1. Scroll to the oldest message in conversation
 2. Mark it as unread
 3. Check unread count</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>All messages in the conversation should be counted as unread</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>ML_214</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Last Message in Chat</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Conversation with messages</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Verify marking the most recent message as unread</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>1. Mark the last/newest received message as unread
 2. Check unread count</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Unread count should show 1, divider should appear before the last message</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ML_215</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Rapid Mark and Open</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Conversation with messages</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Verify rapid mark-unread then immediately open conversation</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Immediately open the same conversation
 3. Scroll to bottom</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Unread state should be set then cleared properly without race conditions</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>ML_216</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - During Active Conversation</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Active conversation with incoming messages</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Verify marking as unread while new messages are arriving</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>1. Be in an active conversation
 2. Mark an older message as unread while new messages arrive</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Mark as unread should work correctly, unread count should include both marked and new messages</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>ML_217</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Multiple Conversations</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Multiple conversations available</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Verify marking messages as unread in multiple conversations</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread in Conversation A
 2. Mark a message as unread in Conversation B
 3. Check conversation list</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Both conversations should show unread badges independently</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>ML_218</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Single Message Conversation</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Conversation with exactly 1 received message</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Verify marking unread in a conversation with only one message</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>1. Open conversation with single received message
 2. Mark it as unread</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Unread count should show 1, conversation should show unread indicator</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>ML_086</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Edge Case: Message List</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Verify message list when WebSocket disconnects</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>1. Simulate WebSocket disconnection during active chat.</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>App should show reconnecting indicator. Messages should sync once reconnected.</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>ML_156</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Forward to Self</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>User tries to forward to themselves</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Verify handling of self-forward</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>1. Try forwarding message to self</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Appropriate handling (allowed or prevented)</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>ML_157</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Unicode in Flag Remark</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Emoji and special chars in remark</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Verify unicode handling in flag remark</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>1. Enter emoji/unicode in remark
-2. Submit</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>Remark saved correctly with unicode</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -8800,67 +8978,102 @@
       <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>ML_219</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Offline State</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Device is offline</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Verify behavior when marking as unread while offline</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>1. Go offline
 2. Try to mark a message as unread
 3. Observe</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Should fail gracefully with error handling, no crash</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A14:H14"/>
+  <mergeCells count="1">
+    <mergeCell ref="A18:H18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8873,7 +9086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9231,237 +9444,237 @@
       <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ML_161</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Quick Options Count 0</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>quickOptionsCount=0</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Verify 0 quick options hides quick menu</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>1. Set quickOptionsCount=0
+2. Hover on message</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>No quick options shown, all in overflow menu</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>ML_220</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Exactly 999 Unread Count</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Conversation with exactly 999 unread messages</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Verify display at 999 boundary</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>1. Have exactly 999 unread messages
 2. Observe badge</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Badge should show '999' (not '999+')</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>ML_221</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - 1000 Unread Count</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Conversation with 1000 unread messages</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Verify display at 1000 boundary</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>1. Have 1000 unread messages
 2. Observe badge</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Badge should show '999+' (cap triggered)</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>ML_222</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Minimum Unread Count (1)</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Single message marked as unread</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Verify minimum unread count display</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>1. Mark exactly 1 message as unread
 2. Observe badge</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Badge should show '1'</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>ML_223</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Zero After Clear</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Previously unread, now scrolled to bottom</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Verify count goes to exactly 0 after clearing</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>1. Have unread messages
 2. Scroll to bottom to clear
 3. Check count</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Unread count should be exactly 0, no badge shown</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>ML_161</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Quick Options Count 0</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>quickOptionsCount=0</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Verify 0 quick options hides quick menu</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>1. Set quickOptionsCount=0
-2. Hover on message</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>No quick options shown, all in overflow menu</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -9490,9 +9703,49 @@
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A13:H13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9505,7 +9758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9967,270 +10220,270 @@
       <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>ML_100</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Verify oversized image (&gt;25MB or above limit)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>1. Try to send an image exceeding the file size limit.</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Error message should display. File should not upload.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
+          <t>ML_166</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Translation - Media Message</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Image/video message</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Verify translation not available for media</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on image message
+2. Check for translate</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Translate option not shown for media messages</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Mark as Unread</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
           <t>ML_224</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Text Message</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Received text message</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread on text message type</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>1. Right-click a received text message
 2. Select Mark as Unread</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Should work correctly for text messages</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>ML_225</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Media Message</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Received media message (image/video/file)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread on media message type</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>1. Right-click a received media message
 2. Select Mark as Unread</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Should work correctly for media messages</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>ML_226</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Custom Message</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Received custom message type</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread on custom message type</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>1. Right-click a received custom message
 2. Select Mark as Unread</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Should work correctly for custom message types</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ML_227</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Middle of Conversation</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Long conversation, message in the middle</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Verify marking a message in the middle of conversation</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>1. Scroll to middle of conversation
 2. Mark a received message as unread</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>All messages after the marked one should count as unread</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>ML_100</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Verify oversized image (&gt;25MB or above limit)</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>1. Try to send an image exceeding the file size limit.</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Error message should display. File should not upload.</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>ML_166</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Translation - Media Message</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Image/video message</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Verify translation not available for media</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on image message
-2. Check for translate</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Translate option not shown for media messages</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -10250,66 +10503,101 @@
       <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>ML_228</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Own Sent Message</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Own sent message in conversation</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread unavailable on own messages</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>1. Right-click own sent message
 2. Check for Mark as Unread option</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Option should NOT be present for sent messages</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A14:H14"/>
+  <mergeCells count="1">
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -4925,13 +4925,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
-      <c r="E117" s="12" t="n"/>
-      <c r="F117" s="12" t="n"/>
-      <c r="G117" s="12" t="n"/>
-      <c r="H117" s="12" t="n"/>
+      <c r="B117" s="11" t="n"/>
+      <c r="C117" s="11" t="n"/>
+      <c r="D117" s="11" t="n"/>
+      <c r="E117" s="11" t="n"/>
+      <c r="F117" s="11" t="n"/>
+      <c r="G117" s="11" t="n"/>
+      <c r="H117" s="11" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
@@ -6511,13 +6511,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -7333,13 +7333,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -7931,13 +7931,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -8698,13 +8698,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -9502,13 +9502,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -10312,13 +10312,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2973,2178 +2973,2178 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
+          <t>ML_114</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Smart Replies</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>showSmartReplies=true, incoming message with question</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Verify smart replies appear for incoming questions</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>1. Receive message containing '?'
+2. Wait for smart replies delay</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Smart reply suggestions appear below message list</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>ML_115</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Smart Replies</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Smart replies visible</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Verify clicking smart reply sends message</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>1. Click on a smart reply suggestion</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Smart reply text sent as message</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>ML_116</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Smart Replies Keywords</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>smartRepliesKeywords=['what','when','how']</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Verify smart replies trigger only for configured keywords</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>1. Receive message with 'what'
+2. Receive message without keywords</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Smart replies appear only for keyword messages</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>ML_117</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Conversation Starters</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>showConversationStarters=true, new chat with no messages</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Verify conversation starters appear in empty chat</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>1. Open new chat with no history</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Conversation starter suggestions displayed</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>ML_118</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Conversation Starters</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Starters visible</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Verify clicking starter sends message</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>1. Click on a conversation starter</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Starter text sent as message, chat begins</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>ML_119</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Moderation View</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>hideModerationView=false, moderated message exists</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Verify moderation status shown on messages</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>1. Send message in moderated group
+2. Check message status</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Moderation status (pending/approved/disapproved) visible</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>ML_120</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Another user typing in chat</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Verify typing indicator appears</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>1. Other user starts typing
+2. Observe message list footer</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>Typing indicator shown with user name</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>ML_121</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Typing Indicators</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>User stops typing</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Verify typing indicator disappears</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>1. Other user stops typing
+2. Wait 500ms</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Typing indicator removed</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>ML_122</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Read/Delivery Receipts</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>hideReceipts=false, message sent</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Verify delivery receipt shown on sent message</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Wait for delivery</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>Double tick/delivered indicator appears</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>ML_123</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Read/Delivery Receipts</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Message delivered and read</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Verify read receipt shown on sent message</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Recipient reads message</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>Blue double tick/read indicator appears</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>ML_124</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Sticky Date Header</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>hideStickyDate=false, scrolling through messages</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Verify sticky date header appears while scrolling</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>1. Open chat with messages across multiple days
+2. Scroll through messages</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>Sticky date header shows current date section</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>ML_125</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Date Separator</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>hideDateSeparator=false</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Verify date separators between different day messages</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>1. Open chat with multi-day messages</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>Date separator labels shown between day groups</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>ML_126</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Scroll to Bottom</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>User scrolled up in message list</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>Verify scroll to bottom button appears</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>1. Scroll up in message list
+2. Check for scroll button</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>Scroll to bottom button visible</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>ML_127</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>New Messages Banner</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>User scrolled up, new message arrives</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>Verify new messages banner appears</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>1. Scroll up
+2. Receive new message</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>New messages banner shown with count</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>ML_128</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Message Information</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>hideMessageInfoOption=false</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Verify message info option shows delivery/read details</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on sent message
+2. Click message info</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>Message info popup shows sent, delivered, read timestamps</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>ML_129</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Go To Message</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>goToMessageId set</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>Verify message list scrolls to specific message</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>1. Set goToMessageId prop
+2. Open message list</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>List scrolls to and highlights the target message</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>ML_167</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - Open Search View</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Conversation open</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>Verify search view opens from header</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>1. Click search icon in message header
+2. Observe side panel</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>CometChatSearchView should open in side panel with search input</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>ML_168</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - Search Messages</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>Verify searching messages in conversation</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>1. Type search query
+2. Observe results</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>CometChatSearch should filter messages by uid/guid with limit 30</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>ML_169</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - Click Result</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Search results displayed</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Verify clicking search result navigates to message</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>1. Search for a message
+2. Click on a result</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>Should navigate to that message in the message list via goToMessageId</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>ML_170</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - Threaded Result</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Search result is a threaded message</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Verify clicking threaded search result opens thread</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>1. Search for a message that's in a thread
+2. Click result</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>Thread should open with the parent message, goToMessageId set to clicked message</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>ML_171</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - Close Search</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Verify closing search view</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>1. Click close button
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Search view should close, showMessagesSearch set to false</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>ML_172</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - Keyword Highlighting</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Search result clicked</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Verify search keyword is highlighted in messages</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>1. Search for 'hello'
+2. Click a result
+3. Observe message list</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>The word 'hello' should be highlighted in the message list using TextHighlightFormatter</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>ML_173</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>AI Chat - Detect Agentic User</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>User with role '@agentic' exists</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Verify AI assistant chat renders for agentic users</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>1. Select a user with role '@agentic'
+2. Observe message view</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>CometChatAIAssistantChat should render instead of regular messages view</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>ML_174</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>AI Chat - Back Button on Mobile</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>AI chat open on mobile</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Verify back button in AI chat on mobile</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>1. Open AI chat on mobile view
+2. Observe back button</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>Back button should be visible (showBackButton=isMobile)</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>ML_175</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>AI Chat - Back Navigation</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>AI chat open</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Verify back button navigates back</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>1. Click back button in AI chat
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Should clear selected item and return to conversation list</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>ML_011</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Verify Message List Display</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in, no messages in conversation</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Verify empty message list state</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>1. Open a new conversation with no messages.</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>ML_018</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Verify Reactions</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>Verify reaction fails without network</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to add a reaction.</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>Error message should display or reaction should queue for retry.</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>ML_030</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Verify Copy Message</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Verify copy not available for media-only messages</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>1. Long press on an image/video message with no caption.</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>ML_034</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Verify Edit Message</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Edit' not available for others' messages</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>'Edit' option should NOT appear for messages sent by other users.</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>ML_042</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Verify Delete Message</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Delete' not available for others' messages</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message.
+2. Observe message menu.</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>ML_047</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Verify Notifications</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>User has notifications disabled</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Verify no notification when disabled</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>1. Disable notifications in settings.
+2. Receive a message.</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>No push notification should appear.</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>ML_130</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Message Translation Hidden</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>hideTranslateMessageOption=true</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Verify translate option hidden when disabled</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions menu</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>Translate option not visible</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>ML_131</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Flag Message Hidden</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>hideFlagMessageOption=true</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Verify flag option hidden when disabled</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions menu</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>Flag message option not visible</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>ML_132</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Message Privately Hidden</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>hideMessagePrivatelyOption=true</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Verify message privately option hidden</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message in group
+2. Check actions</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Message privately option not visible</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>ML_134</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Smart Replies Disabled</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>showSmartReplies=false</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Verify smart replies don't appear</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>1. Receive question message
+2. Wait</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>No smart reply suggestions shown</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>ML_135</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Receipts Hidden</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>hideReceipts=true</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Verify no receipt indicators shown</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>1. Send message
+2. Check for ticks</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>No delivery/read indicators visible</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>ML_136</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Sticky Date Hidden</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>hideStickyDate=true</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Verify sticky date header not shown</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>1. Scroll through messages</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>No sticky date header appears</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>ML_137</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Moderation Hidden</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>hideModerationView=true</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Verify moderation status not shown</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>1. Check moderated messages</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>No moderation status indicators visible</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>ML_138</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Flag Remark Hidden</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>hideFlagRemarkField=true</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Verify remark field hidden in flag dialog</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>1. Click flag option
+2. Check dialog</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>No remark text area in flag dialog</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>ML_139</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Translation Failure</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Network disconnected during translation</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Verify error handling for failed translation</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Click translate</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>Error message shown, original message intact</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>ML_176</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Message Search - No Results</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Search view open</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Verify empty state for no search results</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>1. Search for non-existent text
+2. Observe results</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>Empty state or no results message should be displayed</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>ML_177</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>AI Chat - Non-Agentic User</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>Regular user selected</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Verify regular messages view for non-agentic users</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>1. Select a regular user (role != '@agentic')
+2. Observe view</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>Regular CometChatMessages should render, not AI assistant</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n"/>
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="10" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>Mark as Unread</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="n"/>
+      <c r="C114" s="11" t="n"/>
+      <c r="D114" s="11" t="n"/>
+      <c r="E114" s="11" t="n"/>
+      <c r="F114" s="11" t="n"/>
+      <c r="G114" s="11" t="n"/>
+      <c r="H114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
           <t>ML_112</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>showMarkAsUnreadOption=true</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread option appears</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>1. Open chat
 2. Hover on message
 3. Check for mark as unread</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>Mark as unread option visible in actions</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="H115" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>ML_113</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>Mark as unread option visible</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E116" s="9" t="inlineStr">
         <is>
           <t>Verify marking message as unread works</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F116" s="9" t="inlineStr">
         <is>
           <t>1. Click mark as unread
 2. Go back to conversation list</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="G116" s="9" t="inlineStr">
         <is>
           <t>Conversation shows unread indicator from that message</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H116" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>ML_114</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>Smart Replies</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>showSmartReplies=true, incoming message with question</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>Verify smart replies appear for incoming questions</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>1. Receive message containing '?'
-2. Wait for smart replies delay</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>Smart reply suggestions appear below message list</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>ML_115</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Smart Replies</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>Smart replies visible</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Verify clicking smart reply sends message</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>1. Click on a smart reply suggestion</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>Smart reply text sent as message</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>ML_116</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>Smart Replies Keywords</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>smartRepliesKeywords=['what','when','how']</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>Verify smart replies trigger only for configured keywords</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>1. Receive message with 'what'
-2. Receive message without keywords</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>Smart replies appear only for keyword messages</t>
-        </is>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>ML_117</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>Conversation Starters</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>showConversationStarters=true, new chat with no messages</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>Verify conversation starters appear in empty chat</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>1. Open new chat with no history</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>Conversation starter suggestions displayed</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>ML_118</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>Conversation Starters</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>Starters visible</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>Verify clicking starter sends message</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>1. Click on a conversation starter</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>Starter text sent as message, chat begins</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>ML_119</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>Moderation View</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>hideModerationView=false, moderated message exists</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>Verify moderation status shown on messages</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>1. Send message in moderated group
-2. Check message status</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>Moderation status (pending/approved/disapproved) visible</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>ML_120</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>Typing Indicators</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>Another user typing in chat</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>Verify typing indicator appears</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>1. Other user starts typing
-2. Observe message list footer</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>Typing indicator shown with user name</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>ML_121</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>Typing Indicators</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>User stops typing</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>Verify typing indicator disappears</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>1. Other user stops typing
-2. Wait 500ms</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>Typing indicator removed</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>ML_122</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Read/Delivery Receipts</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>hideReceipts=false, message sent</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>Verify delivery receipt shown on sent message</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>1. Send message
-2. Wait for delivery</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>Double tick/delivered indicator appears</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>ML_123</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>Read/Delivery Receipts</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>Message delivered and read</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>Verify read receipt shown on sent message</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>1. Send message
-2. Recipient reads message</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>Blue double tick/read indicator appears</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>ML_124</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Sticky Date Header</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>hideStickyDate=false, scrolling through messages</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Verify sticky date header appears while scrolling</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>1. Open chat with messages across multiple days
-2. Scroll through messages</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>Sticky date header shows current date section</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>ML_125</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>Date Separator</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>hideDateSeparator=false</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>Verify date separators between different day messages</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>1. Open chat with multi-day messages</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>Date separator labels shown between day groups</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>ML_126</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Scroll to Bottom</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>User scrolled up in message list</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>Verify scroll to bottom button appears</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>1. Scroll up in message list
-2. Check for scroll button</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>Scroll to bottom button visible</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>ML_127</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>New Messages Banner</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>User scrolled up, new message arrives</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>Verify new messages banner appears</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>1. Scroll up
-2. Receive new message</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>New messages banner shown with count</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>ML_128</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>Message Information</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>hideMessageInfoOption=false</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>Verify message info option shows delivery/read details</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on sent message
-2. Click message info</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>Message info popup shows sent, delivered, read timestamps</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>ML_129</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>Go To Message</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>goToMessageId set</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>Verify message list scrolls to specific message</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>1. Set goToMessageId prop
-2. Open message list</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>List scrolls to and highlights the target message</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>ML_167</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - Open Search View</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>Conversation open</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>Verify search view opens from header</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>1. Click search icon in message header
-2. Observe side panel</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>CometChatSearchView should open in side panel with search input</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>ML_168</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - Search Messages</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Search view open</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Verify searching messages in conversation</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>1. Type search query
-2. Observe results</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>CometChatSearch should filter messages by uid/guid with limit 30</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>ML_169</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - Click Result</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>Search results displayed</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>Verify clicking search result navigates to message</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>1. Search for a message
-2. Click on a result</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>Should navigate to that message in the message list via goToMessageId</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>ML_170</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - Threaded Result</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>Search result is a threaded message</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Verify clicking threaded search result opens thread</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>1. Search for a message that's in a thread
-2. Click result</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>Thread should open with the parent message, goToMessageId set to clicked message</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>ML_171</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - Close Search</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>Search view open</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>Verify closing search view</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>1. Click close button
-2. Observe behavior</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>Search view should close, showMessagesSearch set to false</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>ML_172</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - Keyword Highlighting</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>Search result clicked</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>Verify search keyword is highlighted in messages</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>1. Search for 'hello'
-2. Click a result
-3. Observe message list</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>The word 'hello' should be highlighted in the message list using TextHighlightFormatter</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>ML_173</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>AI Chat - Detect Agentic User</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>User with role '@agentic' exists</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>Verify AI assistant chat renders for agentic users</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>1. Select a user with role '@agentic'
-2. Observe message view</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>CometChatAIAssistantChat should render instead of regular messages view</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>ML_174</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>AI Chat - Back Button on Mobile</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>AI chat open on mobile</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>Verify back button in AI chat on mobile</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>1. Open AI chat on mobile view
-2. Observe back button</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>Back button should be visible (showBackButton=isMobile)</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>ML_175</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>AI Chat - Back Navigation</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>AI chat open</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>Verify back button navigates back</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>1. Click back button in AI chat
-2. Observe</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>Should clear selected item and return to conversation list</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="n"/>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="10" t="n"/>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="inlineStr">
-        <is>
-          <t>ML_011</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Verify Message List Display</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in, no messages in conversation</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>Verify empty message list state</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>1. Open a new conversation with no messages.</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>Empty state or placeholder message should display (e.g., 'No messages yet').</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>ML_018</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>Verify Reactions</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>Verify reaction fails without network</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to add a reaction.</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>Error message should display or reaction should queue for retry.</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>ML_030</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Verify Copy Message</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>Verify copy not available for media-only messages</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>1. Long press on an image/video message with no caption.</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>'Copy' option should not appear or be disabled for media-only messages.</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>ML_034</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>Verify Edit Message</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>Verify 'Edit' not available for others' messages</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>'Edit' option should NOT appear for messages sent by other users.</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>ML_042</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Verify Delete Message</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>Verify 'Delete' not available for others' messages</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>1. Long press on another user's message.
-2. Observe message menu.</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>'Delete' option should NOT appear for messages sent by other users (unless admin).</t>
-        </is>
-      </c>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>ML_047</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>Verify Notifications</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>User has notifications disabled</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>Verify no notification when disabled</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>1. Disable notifications in settings.
-2. Receive a message.</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>No push notification should appear.</t>
-        </is>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>ML_130</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Message Translation Hidden</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>hideTranslateMessageOption=true</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Verify translate option hidden when disabled</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message
-2. Check actions menu</t>
-        </is>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>Translate option not visible</t>
-        </is>
-      </c>
-      <c r="H104" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>ML_131</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>Flag Message Hidden</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>hideFlagMessageOption=true</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>Verify flag option hidden when disabled</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message
-2. Check actions menu</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>Flag message option not visible</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>ML_132</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>Message Privately Hidden</t>
-        </is>
-      </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>hideMessagePrivatelyOption=true</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>Verify message privately option hidden</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message in group
-2. Check actions</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>Message privately option not visible</t>
-        </is>
-      </c>
-      <c r="H106" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>ML_133</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>Mark as Unread Hidden</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>showMarkAsUnreadOption=false (default)</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>Verify mark as unread not shown by default</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>1. Hover on message
-2. Check actions</t>
-        </is>
-      </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>Mark as unread option not visible</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>ML_134</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Smart Replies Disabled</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>showSmartReplies=false</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>Verify smart replies don't appear</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>1. Receive question message
-2. Wait</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>No smart reply suggestions shown</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>ML_135</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>Receipts Hidden</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>hideReceipts=true</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>Verify no receipt indicators shown</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>1. Send message
-2. Check for ticks</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>No delivery/read indicators visible</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>ML_136</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Sticky Date Hidden</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>hideStickyDate=true</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>Verify sticky date header not shown</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>1. Scroll through messages</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>No sticky date header appears</t>
-        </is>
-      </c>
-      <c r="H110" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>ML_137</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>Moderation Hidden</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>hideModerationView=true</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>Verify moderation status not shown</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>1. Check moderated messages</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>No moderation status indicators visible</t>
-        </is>
-      </c>
-      <c r="H111" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>ML_138</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>Flag Remark Hidden</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>hideFlagRemarkField=true</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>Verify remark field hidden in flag dialog</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>1. Click flag option
-2. Check dialog</t>
-        </is>
-      </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>No remark text area in flag dialog</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>ML_139</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>Translation Failure</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Network disconnected during translation</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>Verify error handling for failed translation</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>1. Disconnect network
-2. Click translate</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>Error message shown, original message intact</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>ML_176</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>Message Search - No Results</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Search view open</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>Verify empty state for no search results</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>1. Search for non-existent text
-2. Observe results</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>Empty state or no results message should be displayed</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>ML_177</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>AI Chat - Non-Agentic User</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>Regular user selected</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>Verify regular messages view for non-agentic users</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>1. Select a regular user (role != '@agentic')
-2. Observe view</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>Regular CometChatMessages should render, not AI assistant</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="n"/>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-    </row>
     <row r="117">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>Mark as Unread</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="n"/>
-      <c r="C117" s="11" t="n"/>
-      <c r="D117" s="11" t="n"/>
-      <c r="E117" s="11" t="n"/>
-      <c r="F117" s="11" t="n"/>
-      <c r="G117" s="11" t="n"/>
-      <c r="H117" s="11" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>ML_182</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Option Visibility</t>
         </is>
       </c>
-      <c r="D118" s="9" t="inlineStr">
+      <c r="D117" s="9" t="inlineStr">
         <is>
           <t>Message list open, received message visible</t>
         </is>
       </c>
-      <c r="E118" s="9" t="inlineStr">
+      <c r="E117" s="9" t="inlineStr">
         <is>
           <t>Verify 'Mark as Unread' option appears on received messages</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr">
+      <c r="F117" s="9" t="inlineStr">
         <is>
           <t>1. Open a conversation
 2. Right-click/long-press on a received message
 3. Observe context menu options</t>
         </is>
       </c>
-      <c r="G118" s="9" t="inlineStr">
+      <c r="G117" s="9" t="inlineStr">
         <is>
           <t>Mark as Unread option should be visible in the message actions menu</t>
         </is>
       </c>
-      <c r="H118" s="9" t="inlineStr">
+      <c r="H117" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>ML_183</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Execute on Message</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
         <is>
           <t>Received message visible in chat</t>
         </is>
       </c>
-      <c r="E119" s="9" t="inlineStr">
+      <c r="E118" s="9" t="inlineStr">
         <is>
           <t>Verify marking a specific message as unread</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="F118" s="9" t="inlineStr">
         <is>
           <t>1. Right-click/long-press a received message
 2. Select 'Mark as Unread'
 3. Observe changes</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
+      <c r="G118" s="9" t="inlineStr">
         <is>
           <t>Message should be marked as unread, conversation shows unread indicator/badge</t>
         </is>
       </c>
-      <c r="H119" s="9" t="inlineStr">
+      <c r="H118" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>ML_184</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Unread Badge on Conversation</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr">
+      <c r="E119" s="9" t="inlineStr">
         <is>
           <t>Verify unread count badge appears on conversation list</t>
         </is>
       </c>
-      <c r="F120" s="9" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Navigate to conversation list
 3. Observe the conversation entry</t>
         </is>
       </c>
-      <c r="G120" s="9" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>Conversation should show unread count badge (e.g., '1' or the actual unread count)</t>
         </is>
       </c>
-      <c r="H120" s="9" t="inlineStr">
+      <c r="H119" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>ML_185</t>
         </is>
       </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - New Messages Divider</t>
         </is>
       </c>
-      <c r="D121" s="9" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread in chat</t>
         </is>
       </c>
-      <c r="E121" s="9" t="inlineStr">
+      <c r="E120" s="9" t="inlineStr">
         <is>
           <t>Verify 'New Messages' divider appears at the marked position</t>
         </is>
       </c>
-      <c r="F121" s="9" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Re-open the conversation
 3. Observe message list</t>
         </is>
       </c>
-      <c r="G121" s="9" t="inlineStr">
+      <c r="G120" s="9" t="inlineStr">
         <is>
           <t>A 'New Messages' divider line should appear above the marked message, separating read from unread</t>
         </is>
       </c>
-      <c r="H121" s="9" t="inlineStr">
+      <c r="H120" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>ML_186</t>
         </is>
       </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Scroll Position on Reopen</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr">
+      <c r="D121" s="9" t="inlineStr">
         <is>
           <t>Message marked as unread, startFromUnreadMessages enabled</t>
         </is>
       </c>
-      <c r="E122" s="9" t="inlineStr">
+      <c r="E121" s="9" t="inlineStr">
         <is>
           <t>Verify conversation opens at the unread position</t>
         </is>
       </c>
-      <c r="F122" s="9" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Navigate away from conversation
 3. Re-open the same conversation</t>
         </is>
       </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>Message list should scroll to the last read message position, showing unread messages above the divider</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>ML_187</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Mark Unread - Unread Count Display</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>Multiple messages after marked position</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>Verify correct unread count is shown</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>1. Mark a message as unread where 5 messages follow it
+2. Check conversation list badge</t>
+        </is>
+      </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Message list should scroll to the last read message position, showing unread messages above the divider</t>
+          <t>Badge should show the correct unread count (e.g., '5')</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
@@ -5156,7 +5156,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>ML_187</t>
+          <t>ML_188</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -5166,28 +5166,28 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Mark Unread - Unread Count Display</t>
+          <t>Mark Unread - Clear on Scroll to Bottom</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Multiple messages after marked position</t>
+          <t>Unread messages present, banner visible</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>Verify correct unread count is shown</t>
+          <t>Verify unread state clears when user scrolls to bottom</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>1. Mark a message as unread where 5 messages follow it
-2. Check conversation list badge</t>
+          <t>1. Open conversation with unread messages
+2. Scroll to the very bottom of the message list</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>Badge should show the correct unread count (e.g., '5')</t>
+          <t>Unread count should reset to 0, banner disappears, messages marked as read</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>ML_188</t>
+          <t>ML_189</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -5209,239 +5209,196 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Mark Unread - Clear on Scroll to Bottom</t>
+          <t>Mark Unread - Visual Indicator in List</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Unread messages present, banner visible</t>
+          <t>Message marked as unread</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>Verify unread state clears when user scrolls to bottom</t>
+          <t>Verify visual indicator (bold text/dot/badge) on conversation in list</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>1. Open conversation with unread messages
-2. Scroll to the very bottom of the message list</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>Unread count should reset to 0, banner disappears, messages marked as read</t>
-        </is>
-      </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>ML_189</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>Mark Unread - Visual Indicator in List</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>Message marked as unread</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>Verify visual indicator (bold text/dot/badge) on conversation in list</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Go to conversation list
 3. Observe the conversation item</t>
         </is>
       </c>
-      <c r="G125" s="9" t="inlineStr">
+      <c r="G124" s="9" t="inlineStr">
         <is>
           <t>Conversation should have a visual unread indicator (bold title, unread count badge, or dot)</t>
         </is>
       </c>
-      <c r="H125" s="9" t="inlineStr">
+      <c r="H124" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>ML_190</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - New Messages Banner</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>Unread messages exist, user not at bottom</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>Verify new messages banner/count appears in message list</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Open conversation
 3. Observe banner area</t>
         </is>
       </c>
-      <c r="G126" s="9" t="inlineStr">
+      <c r="G125" s="9" t="inlineStr">
         <is>
           <t>A banner showing the unread count (e.g., '3 new messages') should appear, allowing quick scroll to bottom</t>
         </is>
       </c>
-      <c r="H126" s="9" t="inlineStr">
+      <c r="H125" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>ML_191</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - 1:1 User Chat</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>1:1 conversation with received messages</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread works in one-on-one chats</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
+      <c r="F126" s="9" t="inlineStr">
         <is>
           <t>1. Open a 1:1 user conversation
 2. Mark a received message as unread
 3. Check conversation list</t>
         </is>
       </c>
-      <c r="G127" s="9" t="inlineStr">
+      <c r="G126" s="9" t="inlineStr">
         <is>
           <t>Unread badge should appear on the 1:1 conversation</t>
         </is>
       </c>
-      <c r="H127" s="9" t="inlineStr">
+      <c r="H126" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>ML_192</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Group Chat</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>Group conversation with received messages</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread works in group chats</t>
         </is>
       </c>
-      <c r="F128" s="9" t="inlineStr">
+      <c r="F127" s="9" t="inlineStr">
         <is>
           <t>1. Open a group conversation
 2. Mark a received message as unread
 3. Check conversation list</t>
         </is>
       </c>
-      <c r="G128" s="9" t="inlineStr">
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>Unread badge should appear on the group conversation</t>
         </is>
       </c>
-      <c r="H128" s="9" t="inlineStr">
+      <c r="H127" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>ML_193</t>
         </is>
       </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - As Reminder to Reply</t>
         </is>
       </c>
-      <c r="D129" s="9" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>Received message requiring follow-up</t>
         </is>
       </c>
-      <c r="E129" s="9" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>Verify mark as unread serves as a reply reminder</t>
         </is>
       </c>
-      <c r="F129" s="9" t="inlineStr">
+      <c r="F128" s="9" t="inlineStr">
         <is>
           <t>1. Read a message that needs a response later
 2. Mark it as unread
@@ -5449,113 +5406,156 @@
 4. Return to conversation list</t>
         </is>
       </c>
-      <c r="G129" s="9" t="inlineStr">
+      <c r="G128" s="9" t="inlineStr">
         <is>
           <t>Conversation should remain visually prominent with unread indicator until user reads/responds</t>
         </is>
       </c>
-      <c r="H129" s="9" t="inlineStr">
+      <c r="H128" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="9" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>ML_194</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Auto-Clear on Read</t>
         </is>
       </c>
-      <c r="D130" s="9" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>Message previously marked as unread</t>
         </is>
       </c>
-      <c r="E130" s="9" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>Verify unread state clears when user reads the messages</t>
         </is>
       </c>
-      <c r="F130" s="9" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
         <is>
           <t>1. Mark a message as unread
 2. Open the conversation
 3. Scroll through all unread messages to bottom</t>
         </is>
       </c>
-      <c r="G130" s="9" t="inlineStr">
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>Unread indicator should clear, conversation marked as read again</t>
         </is>
       </c>
-      <c r="H130" s="9" t="inlineStr">
+      <c r="H129" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>ML_195</t>
         </is>
       </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
         <is>
           <t>Mark Unread - Count Cap at 999+</t>
         </is>
       </c>
-      <c r="D131" s="9" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>Conversation with 1000+ unread messages</t>
         </is>
       </c>
-      <c r="E131" s="9" t="inlineStr">
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>Verify unread count displays as 999+ for large counts</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F130" s="9" t="inlineStr">
         <is>
           <t>1. Have a conversation with very high unread count
 2. Observe the unread badge</t>
         </is>
       </c>
-      <c r="G131" s="9" t="inlineStr">
+      <c r="G130" s="9" t="inlineStr">
         <is>
           <t>Badge should display '999+' instead of the exact number when count &gt;= 999</t>
         </is>
       </c>
-      <c r="H131" s="9" t="inlineStr">
+      <c r="H130" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="10" t="n"/>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="10" t="n"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
+      <c r="H131" s="10" t="n"/>
+    </row>
     <row r="132">
-      <c r="A132" s="10" t="n"/>
-      <c r="B132" s="10" t="n"/>
-      <c r="C132" s="10" t="n"/>
-      <c r="D132" s="10" t="n"/>
-      <c r="E132" s="10" t="n"/>
-      <c r="F132" s="10" t="n"/>
-      <c r="G132" s="10" t="n"/>
-      <c r="H132" s="10" t="n"/>
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>ML_133</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Mark as Unread Hidden</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>showMarkAsUnreadOption=false (default)</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>Verify mark as unread not shown by default</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>1. Hover on message
+2. Check actions</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>Mark as unread option not visible</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
@@ -5825,9 +5825,49 @@
       <c r="G142" s="10" t="n"/>
       <c r="H142" s="10" t="n"/>
     </row>
+    <row r="143">
+      <c r="A143" s="10" t="n"/>
+      <c r="B143" s="10" t="n"/>
+      <c r="C143" s="10" t="n"/>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="10" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="n"/>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="10" t="n"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="n"/>
+      <c r="B145" s="10" t="n"/>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="10" t="n"/>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="n"/>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="10" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A117:H117"/>
+    <mergeCell ref="A114:H114"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5840,7 +5880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6924,6 +6964,46 @@
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6940,7 +7020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7533,6 +7613,46 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7549,7 +7669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8084,6 +8204,46 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8100,7 +8260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9070,6 +9230,46 @@
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9086,7 +9286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9742,6 +9942,46 @@
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9758,7 +9998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10595,6 +10835,46 @@
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A17:H17"/>

--- a/Message_List/Message_List_Test_Cases.xlsx
+++ b/Message_List/Message_List_Test_Cases.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +158,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4795,13 +4797,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B114" s="11" t="n"/>
-      <c r="C114" s="11" t="n"/>
-      <c r="D114" s="11" t="n"/>
-      <c r="E114" s="11" t="n"/>
-      <c r="F114" s="11" t="n"/>
-      <c r="G114" s="11" t="n"/>
-      <c r="H114" s="11" t="n"/>
+      <c r="B114" s="13" t="n"/>
+      <c r="C114" s="13" t="n"/>
+      <c r="D114" s="13" t="n"/>
+      <c r="E114" s="13" t="n"/>
+      <c r="F114" s="13" t="n"/>
+      <c r="G114" s="13" t="n"/>
+      <c r="H114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -6551,13 +6553,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -7413,13 +7415,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -8051,13 +8053,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -8858,13 +8860,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -9702,13 +9704,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -10552,13 +10554,13 @@
           <t>Mark as Unread</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
